--- a/servers/maze_main_server_dev/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049DC12D-94CE-436C-861F-3EB2B26E9D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAEAD447-3D40-4A02-AA70-C5404DD4D9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1225,12 +1225,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>10104</t>
-  </si>
-  <si>
-    <t>10104,10101</t>
-  </si>
-  <si>
     <t>20104</t>
   </si>
   <si>
@@ -1274,15 +1268,6 @@
   </si>
   <si>
     <t>80109,80106,80103</t>
-  </si>
-  <si>
-    <t>60,50</t>
-  </si>
-  <si>
-    <t>80,60,95,95</t>
-  </si>
-  <si>
-    <t>80,40</t>
   </si>
   <si>
     <t>5,5</t>
@@ -1448,6 +1433,25 @@
   </si>
   <si>
     <t>85,75,75,85,85,20,15,15,10,30,30,10</t>
+  </si>
+  <si>
+    <t>500107,500107,500107</t>
+  </si>
+  <si>
+    <t>500107,500107,500107</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>60,50,50,50,40,50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>80,20,80,10,80,30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30,80,10,80,20,80</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2521,19 +2525,19 @@
         <v>1</v>
       </c>
       <c r="H5" s="12">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="I5" s="12">
         <v>1</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>363</v>
+        <v>434</v>
       </c>
       <c r="K5" s="12">
         <v>20</v>
       </c>
       <c r="L5" s="12">
-        <v>30000</v>
+        <v>100000000</v>
       </c>
       <c r="M5" s="12">
         <v>0</v>
@@ -2542,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>380</v>
+        <v>435</v>
       </c>
       <c r="P5" s="1">
         <v>0</v>
@@ -2571,19 +2575,19 @@
         <v>2</v>
       </c>
       <c r="H6" s="14">
-        <v>5000</v>
+        <v>1</v>
       </c>
       <c r="I6" s="14">
         <v>1</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>364</v>
+        <v>434</v>
       </c>
       <c r="K6" s="14">
         <v>20</v>
       </c>
       <c r="L6" s="14">
-        <v>30000</v>
+        <v>100000000</v>
       </c>
       <c r="M6" s="14">
         <v>0</v>
@@ -2592,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>381</v>
+        <v>436</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
@@ -2621,19 +2625,19 @@
         <v>3</v>
       </c>
       <c r="H7" s="14">
-        <v>10000</v>
+        <v>100000000</v>
       </c>
       <c r="I7" s="14">
         <v>1</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>363</v>
+        <v>433</v>
       </c>
       <c r="K7" s="14">
         <v>20</v>
       </c>
       <c r="L7" s="14">
-        <v>30000</v>
+        <v>100000000</v>
       </c>
       <c r="M7" s="14">
         <v>0</v>
@@ -2642,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>382</v>
+        <v>437</v>
       </c>
       <c r="P7" s="1">
         <v>0</v>
@@ -2677,7 +2681,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="K8" s="12">
         <v>20</v>
@@ -2692,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="P8" s="1">
         <v>0</v>
@@ -2727,7 +2731,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K9" s="14">
         <v>20</v>
@@ -2742,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="P9" s="1">
         <v>0</v>
@@ -2777,7 +2781,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K10" s="14">
         <v>20</v>
@@ -2792,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="P10" s="1">
         <v>0</v>
@@ -2827,7 +2831,7 @@
         <v>3</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="K11" s="12">
         <v>20</v>
@@ -2877,7 +2881,7 @@
         <v>3</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="K12" s="14">
         <v>20</v>
@@ -2892,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="P12" s="1">
         <v>0</v>
@@ -2927,7 +2931,7 @@
         <v>3</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="K13" s="14">
         <v>20</v>
@@ -2942,7 +2946,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="P13" s="1">
         <v>0</v>
@@ -2977,7 +2981,7 @@
         <v>3</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K14" s="16">
         <v>20</v>
@@ -2992,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="P14" s="1">
         <v>0</v>
@@ -3027,7 +3031,7 @@
         <v>4</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K15" s="14">
         <v>20</v>
@@ -3042,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="P15" s="1">
         <v>0</v>
@@ -3077,7 +3081,7 @@
         <v>4</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="K16" s="14">
         <v>20</v>
@@ -3092,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="P16" s="1">
         <v>0</v>
@@ -3127,7 +3131,7 @@
         <v>4</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="K17" s="14">
         <v>20</v>
@@ -3142,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="P17" s="1">
         <v>0</v>
@@ -3177,7 +3181,7 @@
         <v>4</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="K18" s="16">
         <v>20</v>
@@ -3192,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="P18" s="1">
         <v>0</v>
@@ -3292,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="P20" s="1">
         <v>0</v>
@@ -3327,7 +3331,7 @@
         <v>5</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="K21" s="14">
         <v>20</v>
@@ -3342,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="P21" s="1">
         <v>0</v>
@@ -3377,7 +3381,7 @@
         <v>5</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K22" s="16">
         <v>20</v>
@@ -3392,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="P22" s="1">
         <v>0</v>
@@ -3527,7 +3531,7 @@
         <v>6</v>
       </c>
       <c r="J25" s="15" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="K25" s="14">
         <v>20</v>
@@ -3542,7 +3546,7 @@
         <v>1</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="P25" s="1">
         <v>0</v>
@@ -3592,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="P26" s="1">
         <v>0</v>
@@ -3642,7 +3646,7 @@
         <v>1</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="P27" s="1">
         <v>0</v>
@@ -3727,7 +3731,7 @@
         <v>7</v>
       </c>
       <c r="J29" s="15" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K29" s="14">
         <v>20</v>
@@ -3742,7 +3746,7 @@
         <v>1</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="P29" s="1">
         <v>0</v>
@@ -3777,7 +3781,7 @@
         <v>7</v>
       </c>
       <c r="J30" s="15" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="K30" s="14">
         <v>20</v>
@@ -3792,7 +3796,7 @@
         <v>1</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="P30" s="1">
         <v>0</v>
@@ -3827,7 +3831,7 @@
         <v>7</v>
       </c>
       <c r="J31" s="15" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="K31" s="14">
         <v>20</v>
@@ -3842,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="P31" s="1">
         <v>0</v>
@@ -3892,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="P32" s="1">
         <v>0</v>
@@ -4027,7 +4031,7 @@
         <v>8</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="K35" s="14">
         <v>20</v>
@@ -4042,7 +4046,7 @@
         <v>1</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="P35" s="1">
         <v>0</v>
@@ -4077,7 +4081,7 @@
         <v>8</v>
       </c>
       <c r="J36" s="15" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="K36" s="14">
         <v>20</v>
@@ -4092,7 +4096,7 @@
         <v>1</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="P36" s="1">
         <v>0</v>
@@ -4127,7 +4131,7 @@
         <v>8</v>
       </c>
       <c r="J37" s="15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K37" s="14">
         <v>20</v>
@@ -4142,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="P37" s="1">
         <v>0</v>
@@ -4177,7 +4181,7 @@
         <v>8</v>
       </c>
       <c r="J38" s="18" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="K38" s="16">
         <v>20</v>
@@ -4192,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="P38" s="1">
         <v>0</v>
@@ -4227,7 +4231,7 @@
         <v>9</v>
       </c>
       <c r="J39" s="15" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="K39" s="14">
         <v>20</v>
@@ -4242,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="P39" s="1">
         <v>0</v>
@@ -4277,7 +4281,7 @@
         <v>9</v>
       </c>
       <c r="J40" s="15" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="K40" s="14">
         <v>20</v>
@@ -4292,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="P40" s="1">
         <v>0</v>
@@ -4327,7 +4331,7 @@
         <v>9</v>
       </c>
       <c r="J41" s="15" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="K41" s="14">
         <v>20</v>
@@ -4342,7 +4346,7 @@
         <v>1</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="P41" s="1">
         <v>0</v>
@@ -4377,7 +4381,7 @@
         <v>9</v>
       </c>
       <c r="J42" s="15" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="K42" s="14">
         <v>20</v>
@@ -4392,7 +4396,7 @@
         <v>1</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="P42" s="1">
         <v>0</v>
@@ -4427,7 +4431,7 @@
         <v>9</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="K43" s="14">
         <v>20</v>
@@ -4442,7 +4446,7 @@
         <v>1</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="P43" s="1">
         <v>0</v>
@@ -4477,7 +4481,7 @@
         <v>9</v>
       </c>
       <c r="J44" s="15" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="K44" s="14">
         <v>20</v>
@@ -4492,7 +4496,7 @@
         <v>1</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="P44" s="1">
         <v>0</v>
@@ -4527,7 +4531,7 @@
         <v>9</v>
       </c>
       <c r="J45" s="18" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K45" s="16">
         <v>20</v>
@@ -4542,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="P45" s="1">
         <v>0</v>
@@ -4577,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="J46" s="15" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="K46" s="14">
         <v>20</v>
@@ -4592,7 +4596,7 @@
         <v>1</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="P46" s="1">
         <v>0</v>
@@ -4627,7 +4631,7 @@
         <v>10</v>
       </c>
       <c r="J47" s="15" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="K47" s="14">
         <v>20</v>
@@ -4642,7 +4646,7 @@
         <v>1</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="P47" s="1">
         <v>0</v>
@@ -4677,7 +4681,7 @@
         <v>10</v>
       </c>
       <c r="J48" s="15" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="K48" s="14">
         <v>20</v>
@@ -4692,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="P48" s="1">
         <v>0</v>
@@ -4727,7 +4731,7 @@
         <v>10</v>
       </c>
       <c r="J49" s="15" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="K49" s="14">
         <v>20</v>
@@ -4742,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="P49" s="1">
         <v>0</v>
@@ -4777,7 +4781,7 @@
         <v>10</v>
       </c>
       <c r="J50" s="15" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="K50" s="14">
         <v>20</v>
@@ -4792,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="P50" s="1">
         <v>0</v>
@@ -4827,7 +4831,7 @@
         <v>10</v>
       </c>
       <c r="J51" s="15" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="K51" s="14">
         <v>20</v>
@@ -4842,7 +4846,7 @@
         <v>1</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="P51" s="1">
         <v>0</v>
@@ -4877,7 +4881,7 @@
         <v>10</v>
       </c>
       <c r="J52" s="15" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="K52" s="14">
         <v>20</v>
@@ -4892,7 +4896,7 @@
         <v>1</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="P52" s="1">
         <v>0</v>
@@ -4927,7 +4931,7 @@
         <v>10</v>
       </c>
       <c r="J53" s="15" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="K53" s="14">
         <v>20</v>
@@ -4942,7 +4946,7 @@
         <v>1</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="P53" s="1">
         <v>0</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="15580"/>
+    <workbookView windowWidth="27950" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="maze_brush_foe_v8" sheetId="2" r:id="rId1"/>
@@ -1614,12 +1614,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2852,7 +2852,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P1135"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="6" width="14.625" style="2" customWidth="1"/>
     <col min="7" max="7" width="19.5" style="2" customWidth="1"/>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="17.55" spans="1:16">
+    <row r="7" ht="17.25" spans="1:16">
       <c r="A7" s="9">
         <v>110103</v>
       </c>
@@ -3207,8 +3207,8 @@
       <c r="G8" s="8">
         <v>4</v>
       </c>
-      <c r="H8" s="8">
-        <v>4000</v>
+      <c r="H8" s="9">
+        <v>100000000</v>
       </c>
       <c r="I8" s="8">
         <v>2</v>
@@ -3219,8 +3219,8 @@
       <c r="K8" s="8">
         <v>20</v>
       </c>
-      <c r="L8" s="8">
-        <v>30000</v>
+      <c r="L8" s="9">
+        <v>100000000</v>
       </c>
       <c r="M8" s="8">
         <v>0</v>
@@ -3258,7 +3258,7 @@
         <v>5</v>
       </c>
       <c r="H9" s="9">
-        <v>4000</v>
+        <v>100000000</v>
       </c>
       <c r="I9" s="9">
         <v>2</v>
@@ -3270,7 +3270,7 @@
         <v>20</v>
       </c>
       <c r="L9" s="9">
-        <v>30000</v>
+        <v>100000000</v>
       </c>
       <c r="M9" s="9">
         <v>0</v>
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="17.55" spans="1:16">
+    <row r="10" ht="17.25" spans="1:16">
       <c r="A10" s="9">
         <v>110203</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="17.55" spans="1:16">
+    <row r="14" ht="17.25" spans="1:16">
       <c r="A14" s="10">
         <v>110304</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="17.55" spans="1:16">
+    <row r="18" ht="17.25" spans="1:16">
       <c r="A18" s="10">
         <v>110404</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="17.55" spans="1:16">
+    <row r="22" ht="17.25" spans="1:16">
       <c r="A22" s="10">
         <v>110504</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="17.55" spans="1:16">
+    <row r="27" ht="17.25" spans="1:16">
       <c r="A27" s="10">
         <v>110605</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="17.55" spans="1:16">
+    <row r="32" ht="17.25" spans="1:16">
       <c r="A32" s="10">
         <v>110705</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="17.55" spans="1:16">
+    <row r="38" ht="17.25" spans="1:16">
       <c r="A38" s="10">
         <v>110806</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" ht="17.55" spans="1:16">
+    <row r="45" ht="17.25" spans="1:16">
       <c r="A45" s="10">
         <v>110907</v>
       </c>
@@ -5585,7 +5585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" ht="17.55" spans="1:16">
+    <row r="56" ht="17.25" spans="1:16">
       <c r="A56" s="12">
         <v>210103</v>
       </c>
@@ -5735,7 +5735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" ht="17.55" spans="1:16">
+    <row r="59" ht="17.25" spans="1:16">
       <c r="A59" s="12">
         <v>210203</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" ht="17.55" spans="1:16">
+    <row r="63" ht="17.25" spans="1:16">
       <c r="A63" s="12">
         <v>210304</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" ht="17.55" spans="1:16">
+    <row r="67" ht="17.25" spans="1:16">
       <c r="A67" s="12">
         <v>210404</v>
       </c>
@@ -6335,7 +6335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" ht="17.55" spans="1:16">
+    <row r="71" ht="17.25" spans="1:16">
       <c r="A71" s="12">
         <v>210504</v>
       </c>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" ht="17.55" spans="1:16">
+    <row r="76" ht="17.25" spans="1:16">
       <c r="A76" s="12">
         <v>210605</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" ht="17.55" spans="1:16">
+    <row r="81" ht="17.25" spans="1:16">
       <c r="A81" s="12">
         <v>210705</v>
       </c>
@@ -7135,7 +7135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" ht="17.55" spans="1:16">
+    <row r="87" ht="17.25" spans="1:16">
       <c r="A87" s="12">
         <v>210806</v>
       </c>
@@ -7485,7 +7485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" ht="17.55" spans="1:16">
+    <row r="94" ht="17.25" spans="1:16">
       <c r="A94" s="12">
         <v>210907</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" ht="17.55" spans="1:16">
+    <row r="102" ht="17.25" spans="1:16">
       <c r="A102" s="22">
         <v>211008</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" ht="17.55" spans="1:16">
+    <row r="106" ht="17.25" spans="1:16">
       <c r="A106" s="22">
         <v>220104</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" ht="17.55" spans="1:16">
+    <row r="111" ht="17.25" spans="1:16">
       <c r="A111" s="22">
         <v>220205</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" ht="17.55" spans="1:16">
+    <row r="117" ht="17.25" spans="1:16">
       <c r="A117" s="22">
         <v>220306</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" ht="17.55" spans="1:16">
+    <row r="123" ht="17.25" spans="1:16">
       <c r="A123" s="22">
         <v>220406</v>
       </c>
@@ -9235,7 +9235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" ht="17.55" spans="1:16">
+    <row r="129" ht="17.25" spans="1:16">
       <c r="A129" s="22">
         <v>220506</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" ht="17.55" spans="1:16">
+    <row r="136" ht="17.25" spans="1:16">
       <c r="A136" s="22">
         <v>220607</v>
       </c>
@@ -9985,7 +9985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" ht="17.55" spans="1:16">
+    <row r="144" ht="17.25" spans="1:16">
       <c r="A144" s="22">
         <v>220708</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" ht="17.55" spans="1:16">
+    <row r="152" ht="17.25" spans="1:16">
       <c r="A152" s="22">
         <v>220808</v>
       </c>
@@ -10785,7 +10785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" ht="17.55" spans="1:16">
+    <row r="160" ht="17.25" spans="1:16">
       <c r="A160" s="22">
         <v>220908</v>
       </c>
@@ -13635,7 +13635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" ht="17.55" spans="1:16">
+    <row r="217" ht="17.25" spans="1:16">
       <c r="A217" s="26">
         <v>311008</v>
       </c>
@@ -19385,7 +19385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" ht="17.55" spans="1:16">
+    <row r="332" ht="17.25" spans="1:16">
       <c r="A332" s="30">
         <v>411008</v>
       </c>
@@ -22835,7 +22835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" ht="17.55" spans="1:16">
+    <row r="401" ht="17.25" spans="1:16">
       <c r="A401" s="33">
         <v>510103</v>
       </c>
@@ -22985,7 +22985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" ht="17.55" spans="1:16">
+    <row r="404" ht="17.25" spans="1:16">
       <c r="A404" s="33">
         <v>510203</v>
       </c>
@@ -23185,7 +23185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" ht="17.55" spans="1:16">
+    <row r="408" ht="17.25" spans="1:16">
       <c r="A408" s="33">
         <v>510304</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" ht="17.55" spans="1:16">
+    <row r="412" ht="17.25" spans="1:16">
       <c r="A412" s="33">
         <v>510404</v>
       </c>
@@ -23635,7 +23635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" ht="17.55" spans="1:16">
+    <row r="417" ht="17.25" spans="1:16">
       <c r="A417" s="33">
         <v>510505</v>
       </c>
@@ -23935,7 +23935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" ht="17.55" spans="1:16">
+    <row r="423" ht="17.25" spans="1:16">
       <c r="A423" s="33">
         <v>510606</v>
       </c>
@@ -24235,7 +24235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" ht="17.55" spans="1:16">
+    <row r="429" ht="17.25" spans="1:16">
       <c r="A429" s="33">
         <v>510706</v>
       </c>
@@ -24585,7 +24585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" ht="17.55" spans="1:16">
+    <row r="436" ht="17.25" spans="1:16">
       <c r="A436" s="33">
         <v>510807</v>
       </c>
@@ -24985,7 +24985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" ht="17.55" spans="1:16">
+    <row r="444" ht="17.25" spans="1:16">
       <c r="A444" s="33">
         <v>510908</v>
       </c>
@@ -25435,7 +25435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" ht="17.55" spans="1:16">
+    <row r="453" ht="17.25" spans="1:16">
       <c r="A453" s="26">
         <v>511009</v>
       </c>
@@ -25585,7 +25585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" ht="17.55" spans="1:16">
+    <row r="456" ht="17.25" spans="1:16">
       <c r="A456" s="36">
         <v>520103</v>
       </c>
@@ -25785,7 +25785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" ht="17.55" spans="1:16">
+    <row r="460" ht="17.25" spans="1:16">
       <c r="A460" s="37">
         <v>520204</v>
       </c>
@@ -26035,7 +26035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" ht="17.55" spans="1:16">
+    <row r="465" ht="17.25" spans="1:16">
       <c r="A465" s="33">
         <v>520305</v>
       </c>
@@ -26335,7 +26335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" ht="17.55" spans="1:16">
+    <row r="471" ht="17.25" spans="1:16">
       <c r="A471" s="33">
         <v>520406</v>
       </c>
@@ -26685,7 +26685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" ht="17.55" spans="1:16">
+    <row r="478" ht="17.25" spans="1:16">
       <c r="A478" s="33">
         <v>520507</v>
       </c>
@@ -27085,7 +27085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" ht="17.55" spans="1:16">
+    <row r="486" ht="17.25" spans="1:16">
       <c r="A486" s="33">
         <v>520608</v>
       </c>
@@ -27585,7 +27585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" ht="17.55" spans="1:16">
+    <row r="496" ht="17.25" spans="1:16">
       <c r="A496" s="33">
         <v>520710</v>
       </c>
@@ -28135,7 +28135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" ht="17.55" spans="1:16">
+    <row r="507" ht="17.25" spans="1:16">
       <c r="A507" s="33">
         <v>520811</v>
       </c>
@@ -28735,7 +28735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" ht="17.55" spans="1:16">
+    <row r="519" ht="17.25" spans="1:16">
       <c r="A519" s="33">
         <v>520912</v>
       </c>
@@ -29335,7 +29335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" ht="17.55" spans="1:16">
+    <row r="531" ht="17.25" spans="1:16">
       <c r="A531" s="40">
         <v>521012</v>
       </c>
@@ -36235,7 +36235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" ht="17.55" spans="1:16">
+    <row r="669" ht="17.25" spans="1:16">
       <c r="A669" s="50">
         <v>611009</v>
       </c>
@@ -40135,7 +40135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="747" s="1" customFormat="1" ht="17.55" spans="1:16">
+    <row r="747" s="1" customFormat="1" ht="17.25" spans="1:16">
       <c r="A747" s="53">
         <v>621012</v>
       </c>
@@ -46385,7 +46385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="872" ht="17.55" spans="1:16">
+    <row r="872" ht="17.25" spans="1:16">
       <c r="A872" s="56">
         <v>710904</v>
       </c>
@@ -47035,7 +47035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="885" ht="17.55" spans="1:16">
+    <row r="885" ht="17.25" spans="1:16">
       <c r="A885" s="56">
         <v>711009</v>
       </c>
@@ -50935,7 +50935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="963" ht="17.55" spans="1:16">
+    <row r="963" ht="17.25" spans="1:16">
       <c r="A963" s="63">
         <v>721012</v>
       </c>

--- a/servers/maze_main_server_dev/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90A834B-64FC-4D27-8CF4-95A396687B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E90E1A5-D996-4264-B65A-88FA9941BAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2311" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2311" uniqueCount="474">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1429,21 +1429,139 @@
     <t>100106</t>
   </si>
   <si>
-    <t>10104</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>10104,10101</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>60,50</t>
   </si>
   <si>
-    <t>80,60,95,95</t>
+    <t>80,40</t>
   </si>
   <si>
-    <t>80,40</t>
+    <t>80,60,90,90</t>
+  </si>
+  <si>
+    <t>80,50</t>
+  </si>
+  <si>
+    <t>50,5,15,85</t>
+  </si>
+  <si>
+    <t>5,50,10,90</t>
+  </si>
+  <si>
+    <t>30,20,20,30</t>
+  </si>
+  <si>
+    <t>55,45,90,20</t>
+  </si>
+  <si>
+    <t>45,55,80,10</t>
+  </si>
+  <si>
+    <t>40,40,55,45,45,55</t>
+  </si>
+  <si>
+    <t>85,15,75,25</t>
+  </si>
+  <si>
+    <t>55,45,45,55,80,20</t>
+  </si>
+  <si>
+    <t>60,40,40,60</t>
+  </si>
+  <si>
+    <t>10,40,15,45,90,90</t>
+  </si>
+  <si>
+    <t>20,35,90,80,80,90</t>
+  </si>
+  <si>
+    <t>10,40,15,45</t>
+  </si>
+  <si>
+    <t>10,50,15,55,85,85</t>
+  </si>
+  <si>
+    <t>20,45,85,75,75,85</t>
+  </si>
+  <si>
+    <t>10,60,15,65</t>
+  </si>
+  <si>
+    <t>20,60,25,65,80,80</t>
+  </si>
+  <si>
+    <t>15,60,75,75</t>
+  </si>
+  <si>
+    <t>20,50,50,20,10,20</t>
+  </si>
+  <si>
+    <t>40,40,15,25,25,15</t>
+  </si>
+  <si>
+    <t>15,55,55,15</t>
+  </si>
+  <si>
+    <t>45,45,20,25,25,20</t>
+  </si>
+  <si>
+    <t>20,60,60,20,40,40</t>
+  </si>
+  <si>
+    <t>45,45,25,30,30,25</t>
+  </si>
+  <si>
+    <t>50,50,20,60,60,20</t>
+  </si>
+  <si>
+    <t>45,45,10,40,40,10</t>
+  </si>
+  <si>
+    <t>55,55,20,60,60,20</t>
+  </si>
+  <si>
+    <t>50,50,15,45,45,15</t>
+  </si>
+  <si>
+    <t>45,45,10,50,50,10</t>
+  </si>
+  <si>
+    <t>71104</t>
+  </si>
+  <si>
+    <t>71104,71101</t>
+  </si>
+  <si>
+    <t>71104,71104</t>
+  </si>
+  <si>
+    <t>71107,71104,71104</t>
+  </si>
+  <si>
+    <t>71101,71101</t>
+  </si>
+  <si>
+    <t>71104,71104,71101</t>
+  </si>
+  <si>
+    <t>71105,71105,71102</t>
+  </si>
+  <si>
+    <t>71108,71102,71102</t>
+  </si>
+  <si>
+    <t>71105,71105</t>
+  </si>
+  <si>
+    <t>71105,71102</t>
+  </si>
+  <si>
+    <t>71105,71105,71105</t>
+  </si>
+  <si>
+    <t>71105,71102,71102</t>
+  </si>
+  <si>
+    <t>71108,71105,71105</t>
   </si>
 </sst>
 </file>
@@ -1535,7 +1653,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1593,6 +1711,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1766,7 +1890,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1991,6 +2115,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -43823,22 +43956,22 @@
         <v>1</v>
       </c>
       <c r="J831" s="61" t="s">
+        <v>461</v>
+      </c>
+      <c r="K831" s="60">
+        <v>20</v>
+      </c>
+      <c r="L831" s="60">
+        <v>30000</v>
+      </c>
+      <c r="M831" s="60">
+        <v>0</v>
+      </c>
+      <c r="N831" s="1">
+        <v>0</v>
+      </c>
+      <c r="O831" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="K831" s="60">
-        <v>20</v>
-      </c>
-      <c r="L831" s="60">
-        <v>30000</v>
-      </c>
-      <c r="M831" s="60">
-        <v>0</v>
-      </c>
-      <c r="N831" s="1">
-        <v>0</v>
-      </c>
-      <c r="O831" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="P831" s="1">
         <v>0</v>
@@ -43873,7 +44006,7 @@
         <v>1</v>
       </c>
       <c r="J832" s="61" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
       <c r="K832" s="60">
         <v>20</v>
@@ -43888,7 +44021,7 @@
         <v>0</v>
       </c>
       <c r="O832" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P832" s="1">
         <v>0</v>
@@ -43923,7 +44056,7 @@
         <v>1</v>
       </c>
       <c r="J833" s="61" t="s">
-        <v>429</v>
+        <v>461</v>
       </c>
       <c r="K833" s="60">
         <v>20</v>
@@ -43938,7 +44071,7 @@
         <v>0</v>
       </c>
       <c r="O833" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="P833" s="1">
         <v>0</v>
@@ -43973,7 +44106,7 @@
         <v>2</v>
       </c>
       <c r="J834" s="61" t="s">
-        <v>351</v>
+        <v>461</v>
       </c>
       <c r="K834" s="60">
         <v>20</v>
@@ -43988,7 +44121,7 @@
         <v>0</v>
       </c>
       <c r="O834" s="1" t="s">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="P834" s="1">
         <v>0</v>
@@ -44023,7 +44156,7 @@
         <v>2</v>
       </c>
       <c r="J835" s="61" t="s">
-        <v>352</v>
+        <v>462</v>
       </c>
       <c r="K835" s="60">
         <v>20</v>
@@ -44038,7 +44171,7 @@
         <v>0</v>
       </c>
       <c r="O835" s="1" t="s">
-        <v>367</v>
+        <v>433</v>
       </c>
       <c r="P835" s="1">
         <v>0</v>
@@ -44067,13 +44200,13 @@
         <v>6</v>
       </c>
       <c r="H836" s="60">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="I836" s="60">
         <v>2</v>
       </c>
       <c r="J836" s="61" t="s">
-        <v>352</v>
+        <v>462</v>
       </c>
       <c r="K836" s="60">
         <v>20</v>
@@ -44088,7 +44221,7 @@
         <v>0</v>
       </c>
       <c r="O836" s="1" t="s">
-        <v>368</v>
+        <v>434</v>
       </c>
       <c r="P836" s="1">
         <v>0</v>
@@ -44117,13 +44250,13 @@
         <v>7</v>
       </c>
       <c r="H837" s="60">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="I837" s="60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J837" s="61" t="s">
-        <v>353</v>
+        <v>463</v>
       </c>
       <c r="K837" s="60">
         <v>20</v>
@@ -44138,7 +44271,7 @@
         <v>0</v>
       </c>
       <c r="O837" s="1" t="s">
-        <v>178</v>
+        <v>435</v>
       </c>
       <c r="P837" s="1">
         <v>0</v>
@@ -44167,13 +44300,13 @@
         <v>8</v>
       </c>
       <c r="H838" s="60">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I838" s="60">
         <v>3</v>
       </c>
       <c r="J838" s="61" t="s">
-        <v>354</v>
+        <v>462</v>
       </c>
       <c r="K838" s="60">
         <v>20</v>
@@ -44188,7 +44321,7 @@
         <v>0</v>
       </c>
       <c r="O838" s="1" t="s">
-        <v>369</v>
+        <v>436</v>
       </c>
       <c r="P838" s="1">
         <v>0</v>
@@ -44223,7 +44356,7 @@
         <v>3</v>
       </c>
       <c r="J839" s="61" t="s">
-        <v>353</v>
+        <v>462</v>
       </c>
       <c r="K839" s="60">
         <v>20</v>
@@ -44238,7 +44371,7 @@
         <v>0</v>
       </c>
       <c r="O839" s="1" t="s">
-        <v>370</v>
+        <v>437</v>
       </c>
       <c r="P839" s="1">
         <v>0</v>
@@ -44267,13 +44400,13 @@
         <v>10</v>
       </c>
       <c r="H840" s="60">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="I840" s="60">
         <v>3</v>
       </c>
       <c r="J840" s="61" t="s">
-        <v>355</v>
+        <v>464</v>
       </c>
       <c r="K840" s="60">
         <v>20</v>
@@ -44288,7 +44421,7 @@
         <v>0</v>
       </c>
       <c r="O840" s="1" t="s">
-        <v>371</v>
+        <v>438</v>
       </c>
       <c r="P840" s="1">
         <v>0</v>
@@ -44320,10 +44453,10 @@
         <v>3500</v>
       </c>
       <c r="I841" s="60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J841" s="61" t="s">
-        <v>356</v>
+        <v>465</v>
       </c>
       <c r="K841" s="60">
         <v>20</v>
@@ -44338,7 +44471,7 @@
         <v>0</v>
       </c>
       <c r="O841" s="1" t="s">
-        <v>372</v>
+        <v>439</v>
       </c>
       <c r="P841" s="1">
         <v>0</v>
@@ -44370,10 +44503,10 @@
         <v>5000</v>
       </c>
       <c r="I842" s="60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J842" s="61" t="s">
-        <v>356</v>
+        <v>466</v>
       </c>
       <c r="K842" s="60">
         <v>20</v>
@@ -44388,7 +44521,7 @@
         <v>0</v>
       </c>
       <c r="O842" s="1" t="s">
-        <v>373</v>
+        <v>440</v>
       </c>
       <c r="P842" s="1">
         <v>0</v>
@@ -44417,13 +44550,13 @@
         <v>13</v>
       </c>
       <c r="H843" s="60">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="I843" s="60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J843" s="61" t="s">
-        <v>357</v>
+        <v>463</v>
       </c>
       <c r="K843" s="60">
         <v>20</v>
@@ -44438,7 +44571,7 @@
         <v>0</v>
       </c>
       <c r="O843" s="1" t="s">
-        <v>374</v>
+        <v>441</v>
       </c>
       <c r="P843" s="1">
         <v>0</v>
@@ -44467,13 +44600,13 @@
         <v>14</v>
       </c>
       <c r="H844" s="60">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="I844" s="60">
         <v>4</v>
       </c>
       <c r="J844" s="61" t="s">
-        <v>358</v>
+        <v>467</v>
       </c>
       <c r="K844" s="60">
         <v>20</v>
@@ -44488,7 +44621,7 @@
         <v>0</v>
       </c>
       <c r="O844" s="1" t="s">
-        <v>375</v>
+        <v>442</v>
       </c>
       <c r="P844" s="1">
         <v>0</v>
@@ -44517,13 +44650,13 @@
         <v>15</v>
       </c>
       <c r="H845" s="60">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="I845" s="60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J845" s="61" t="s">
-        <v>162</v>
+        <v>468</v>
       </c>
       <c r="K845" s="60">
         <v>20</v>
@@ -44538,7 +44671,7 @@
         <v>0</v>
       </c>
       <c r="O845" s="1" t="s">
-        <v>179</v>
+        <v>443</v>
       </c>
       <c r="P845" s="1">
         <v>0</v>
@@ -44567,13 +44700,13 @@
         <v>16</v>
       </c>
       <c r="H846" s="60">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="I846" s="60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J846" s="61" t="s">
-        <v>163</v>
+        <v>469</v>
       </c>
       <c r="K846" s="60">
         <v>20</v>
@@ -44588,7 +44721,7 @@
         <v>0</v>
       </c>
       <c r="O846" s="1" t="s">
-        <v>390</v>
+        <v>444</v>
       </c>
       <c r="P846" s="1">
         <v>0</v>
@@ -44617,13 +44750,13 @@
         <v>17</v>
       </c>
       <c r="H847" s="60">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="I847" s="60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J847" s="61" t="s">
-        <v>359</v>
+        <v>467</v>
       </c>
       <c r="K847" s="60">
         <v>20</v>
@@ -44638,7 +44771,7 @@
         <v>0</v>
       </c>
       <c r="O847" s="1" t="s">
-        <v>376</v>
+        <v>445</v>
       </c>
       <c r="P847" s="1">
         <v>0</v>
@@ -44667,13 +44800,13 @@
         <v>18</v>
       </c>
       <c r="H848" s="60">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="I848" s="60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J848" s="61" t="s">
-        <v>360</v>
+        <v>468</v>
       </c>
       <c r="K848" s="60">
         <v>20</v>
@@ -44688,7 +44821,7 @@
         <v>0</v>
       </c>
       <c r="O848" s="1" t="s">
-        <v>377</v>
+        <v>446</v>
       </c>
       <c r="P848" s="1">
         <v>0</v>
@@ -44717,13 +44850,13 @@
         <v>19</v>
       </c>
       <c r="H849" s="60">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I849" s="60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J849" s="61" t="s">
-        <v>146</v>
+        <v>469</v>
       </c>
       <c r="K849" s="60">
         <v>20</v>
@@ -44738,7 +44871,7 @@
         <v>0</v>
       </c>
       <c r="O849" s="1" t="s">
-        <v>180</v>
+        <v>447</v>
       </c>
       <c r="P849" s="1">
         <v>0</v>
@@ -44767,13 +44900,13 @@
         <v>20</v>
       </c>
       <c r="H850" s="60">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="I850" s="60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J850" s="61" t="s">
-        <v>164</v>
+        <v>467</v>
       </c>
       <c r="K850" s="60">
         <v>20</v>
@@ -44788,7 +44921,7 @@
         <v>0</v>
       </c>
       <c r="O850" s="1" t="s">
-        <v>183</v>
+        <v>448</v>
       </c>
       <c r="P850" s="1">
         <v>0</v>
@@ -44817,13 +44950,13 @@
         <v>21</v>
       </c>
       <c r="H851" s="60">
-        <v>4500</v>
+        <v>10000</v>
       </c>
       <c r="I851" s="60">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J851" s="61" t="s">
-        <v>361</v>
+        <v>470</v>
       </c>
       <c r="K851" s="60">
         <v>20</v>
@@ -44838,7 +44971,7 @@
         <v>0</v>
       </c>
       <c r="O851" s="1" t="s">
-        <v>378</v>
+        <v>449</v>
       </c>
       <c r="P851" s="1">
         <v>0</v>
@@ -44870,10 +45003,10 @@
         <v>3000</v>
       </c>
       <c r="I852" s="60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J852" s="61" t="s">
-        <v>165</v>
+        <v>467</v>
       </c>
       <c r="K852" s="60">
         <v>20</v>
@@ -44888,7 +45021,7 @@
         <v>0</v>
       </c>
       <c r="O852" s="1" t="s">
-        <v>379</v>
+        <v>450</v>
       </c>
       <c r="P852" s="1">
         <v>0</v>
@@ -44917,13 +45050,13 @@
         <v>23</v>
       </c>
       <c r="H853" s="60">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I853" s="60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J853" s="61" t="s">
-        <v>165</v>
+        <v>468</v>
       </c>
       <c r="K853" s="60">
         <v>20</v>
@@ -44938,7 +45071,7 @@
         <v>0</v>
       </c>
       <c r="O853" s="1" t="s">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="P853" s="1">
         <v>0</v>
@@ -44970,10 +45103,10 @@
         <v>2500</v>
       </c>
       <c r="I854" s="60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J854" s="61" t="s">
-        <v>166</v>
+        <v>469</v>
       </c>
       <c r="K854" s="60">
         <v>20</v>
@@ -44988,7 +45121,7 @@
         <v>0</v>
       </c>
       <c r="O854" s="1" t="s">
-        <v>184</v>
+        <v>452</v>
       </c>
       <c r="P854" s="1">
         <v>0</v>
@@ -45017,13 +45150,13 @@
         <v>25</v>
       </c>
       <c r="H855" s="60">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="I855" s="60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J855" s="61" t="s">
-        <v>362</v>
+        <v>468</v>
       </c>
       <c r="K855" s="60">
         <v>20</v>
@@ -45038,7 +45171,7 @@
         <v>0</v>
       </c>
       <c r="O855" s="1" t="s">
-        <v>381</v>
+        <v>453</v>
       </c>
       <c r="P855" s="1">
         <v>0</v>
@@ -45070,10 +45203,10 @@
         <v>3000</v>
       </c>
       <c r="I856" s="60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J856" s="61" t="s">
-        <v>363</v>
+        <v>471</v>
       </c>
       <c r="K856" s="60">
         <v>20</v>
@@ -45088,7 +45221,7 @@
         <v>0</v>
       </c>
       <c r="O856" s="1" t="s">
-        <v>382</v>
+        <v>454</v>
       </c>
       <c r="P856" s="1">
         <v>0</v>
@@ -45120,10 +45253,10 @@
         <v>3000</v>
       </c>
       <c r="I857" s="60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J857" s="61" t="s">
-        <v>363</v>
+        <v>472</v>
       </c>
       <c r="K857" s="60">
         <v>20</v>
@@ -45138,7 +45271,7 @@
         <v>0</v>
       </c>
       <c r="O857" s="1" t="s">
-        <v>383</v>
+        <v>455</v>
       </c>
       <c r="P857" s="1">
         <v>0</v>
@@ -45167,13 +45300,13 @@
         <v>28</v>
       </c>
       <c r="H858" s="60">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="I858" s="60">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J858" s="61" t="s">
-        <v>167</v>
+        <v>473</v>
       </c>
       <c r="K858" s="60">
         <v>20</v>
@@ -45188,7 +45321,7 @@
         <v>0</v>
       </c>
       <c r="O858" s="1" t="s">
-        <v>384</v>
+        <v>456</v>
       </c>
       <c r="P858" s="1">
         <v>0</v>
@@ -45217,13 +45350,13 @@
         <v>29</v>
       </c>
       <c r="H859" s="60">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I859" s="60">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J859" s="61" t="s">
-        <v>147</v>
+        <v>472</v>
       </c>
       <c r="K859" s="60">
         <v>20</v>
@@ -45238,7 +45371,7 @@
         <v>0</v>
       </c>
       <c r="O859" s="1" t="s">
-        <v>185</v>
+        <v>457</v>
       </c>
       <c r="P859" s="1">
         <v>0</v>
@@ -45270,10 +45403,10 @@
         <v>4000</v>
       </c>
       <c r="I860" s="60">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J860" s="61" t="s">
-        <v>168</v>
+        <v>473</v>
       </c>
       <c r="K860" s="60">
         <v>20</v>
@@ -45288,7 +45421,7 @@
         <v>0</v>
       </c>
       <c r="O860" s="1" t="s">
-        <v>186</v>
+        <v>458</v>
       </c>
       <c r="P860" s="1">
         <v>0</v>
@@ -45317,13 +45450,13 @@
         <v>31</v>
       </c>
       <c r="H861" s="60">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I861" s="60">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J861" s="61" t="s">
-        <v>364</v>
+        <v>472</v>
       </c>
       <c r="K861" s="60">
         <v>20</v>
@@ -45338,7 +45471,7 @@
         <v>0</v>
       </c>
       <c r="O861" s="1" t="s">
-        <v>385</v>
+        <v>459</v>
       </c>
       <c r="P861" s="1">
         <v>0</v>
@@ -45367,80 +45500,80 @@
         <v>32</v>
       </c>
       <c r="H862" s="60">
+        <v>1</v>
+      </c>
+      <c r="I862" s="60">
+        <v>5</v>
+      </c>
+      <c r="J862" s="61" t="s">
+        <v>472</v>
+      </c>
+      <c r="K862" s="60">
+        <v>20</v>
+      </c>
+      <c r="L862" s="60">
+        <v>30000</v>
+      </c>
+      <c r="M862" s="60">
+        <v>0</v>
+      </c>
+      <c r="N862" s="1">
+        <v>0</v>
+      </c>
+      <c r="O862" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="P862" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="863" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A863" s="76">
+        <v>710802</v>
+      </c>
+      <c r="B863" s="76">
+        <v>7</v>
+      </c>
+      <c r="C863" s="76">
+        <v>7000101</v>
+      </c>
+      <c r="D863" s="76">
+        <v>1</v>
+      </c>
+      <c r="E863" s="76">
+        <v>70001</v>
+      </c>
+      <c r="F863" s="76">
+        <v>1</v>
+      </c>
+      <c r="G863" s="76">
+        <v>33</v>
+      </c>
+      <c r="H863" s="76">
         <v>3000</v>
       </c>
-      <c r="I862" s="60">
-        <v>8</v>
-      </c>
-      <c r="J862" s="61" t="s">
-        <v>387</v>
-      </c>
-      <c r="K862" s="60">
-        <v>20</v>
-      </c>
-      <c r="L862" s="60">
-        <v>30000</v>
-      </c>
-      <c r="M862" s="60">
-        <v>0</v>
-      </c>
-      <c r="N862" s="1">
-        <v>0</v>
-      </c>
-      <c r="O862" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="P862" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="863" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A863" s="60">
-        <v>710802</v>
-      </c>
-      <c r="B863" s="60">
-        <v>7</v>
-      </c>
-      <c r="C863" s="60">
-        <v>7000101</v>
-      </c>
-      <c r="D863" s="60">
-        <v>1</v>
-      </c>
-      <c r="E863" s="60">
-        <v>70001</v>
-      </c>
-      <c r="F863" s="60">
-        <v>1</v>
-      </c>
-      <c r="G863" s="60">
-        <v>33</v>
-      </c>
-      <c r="H863" s="60">
-        <v>3000</v>
-      </c>
-      <c r="I863" s="60">
-        <v>8</v>
-      </c>
-      <c r="J863" s="61" t="s">
+      <c r="I863" s="76">
+        <v>6</v>
+      </c>
+      <c r="J863" s="77" t="s">
         <v>365</v>
       </c>
-      <c r="K863" s="60">
-        <v>20</v>
-      </c>
-      <c r="L863" s="60">
-        <v>30000</v>
-      </c>
-      <c r="M863" s="60">
-        <v>0</v>
-      </c>
-      <c r="N863" s="1">
-        <v>0</v>
-      </c>
-      <c r="O863" s="1" t="s">
+      <c r="K863" s="76">
+        <v>20</v>
+      </c>
+      <c r="L863" s="76">
+        <v>30000</v>
+      </c>
+      <c r="M863" s="76">
+        <v>0</v>
+      </c>
+      <c r="N863" s="78">
+        <v>1</v>
+      </c>
+      <c r="O863" s="78" t="s">
         <v>386</v>
       </c>
-      <c r="P863" s="1">
+      <c r="P863" s="78">
         <v>0</v>
       </c>
     </row>
@@ -45470,7 +45603,7 @@
         <v>5000</v>
       </c>
       <c r="I864" s="60">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J864" s="61" t="s">
         <v>391</v>
@@ -45485,7 +45618,7 @@
         <v>0</v>
       </c>
       <c r="N864" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O864" s="1" t="s">
         <v>411</v>
@@ -45520,7 +45653,7 @@
         <v>3000</v>
       </c>
       <c r="I865" s="60">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J865" s="61" t="s">
         <v>392</v>
@@ -45535,7 +45668,7 @@
         <v>0</v>
       </c>
       <c r="N865" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O865" s="1" t="s">
         <v>412</v>
@@ -45570,7 +45703,7 @@
         <v>3000</v>
       </c>
       <c r="I866" s="60">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J866" s="61" t="s">
         <v>393</v>
@@ -45585,7 +45718,7 @@
         <v>0</v>
       </c>
       <c r="N866" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O866" s="1" t="s">
         <v>413</v>
@@ -45620,7 +45753,7 @@
         <v>3000</v>
       </c>
       <c r="I867" s="60">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J867" s="61" t="s">
         <v>388</v>
@@ -45635,7 +45768,7 @@
         <v>0</v>
       </c>
       <c r="N867" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O867" s="1" t="s">
         <v>414</v>
@@ -45670,7 +45803,7 @@
         <v>3000</v>
       </c>
       <c r="I868" s="60">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J868" s="61" t="s">
         <v>394</v>
@@ -45685,7 +45818,7 @@
         <v>0</v>
       </c>
       <c r="N868" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O868" s="1" t="s">
         <v>415</v>
@@ -45720,7 +45853,7 @@
         <v>3000</v>
       </c>
       <c r="I869" s="60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J869" s="61" t="s">
         <v>393</v>
@@ -45735,7 +45868,7 @@
         <v>0</v>
       </c>
       <c r="N869" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O869" s="1" t="s">
         <v>416</v>
@@ -45770,7 +45903,7 @@
         <v>4000</v>
       </c>
       <c r="I870" s="60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J870" s="61" t="s">
         <v>395</v>
@@ -45785,7 +45918,7 @@
         <v>0</v>
       </c>
       <c r="N870" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O870" s="1" t="s">
         <v>417</v>
@@ -45820,7 +45953,7 @@
         <v>5000</v>
       </c>
       <c r="I871" s="60">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J871" s="61" t="s">
         <v>396</v>
@@ -45835,7 +45968,7 @@
         <v>0</v>
       </c>
       <c r="N871" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O871" s="1" t="s">
         <v>405</v>
@@ -45870,7 +46003,7 @@
         <v>3000</v>
       </c>
       <c r="I872" s="60">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J872" s="61" t="s">
         <v>397</v>
@@ -45885,7 +46018,7 @@
         <v>0</v>
       </c>
       <c r="N872" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O872" s="1" t="s">
         <v>418</v>
@@ -45920,7 +46053,7 @@
         <v>3000</v>
       </c>
       <c r="I873" s="60">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J873" s="61" t="s">
         <v>398</v>
@@ -45935,7 +46068,7 @@
         <v>0</v>
       </c>
       <c r="N873" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O873" s="1" t="s">
         <v>406</v>
@@ -45970,7 +46103,7 @@
         <v>3000</v>
       </c>
       <c r="I874" s="60">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J874" s="61" t="s">
         <v>399</v>
@@ -45985,7 +46118,7 @@
         <v>0</v>
       </c>
       <c r="N874" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O874" s="1" t="s">
         <v>419</v>
@@ -46035,7 +46168,7 @@
         <v>0</v>
       </c>
       <c r="N875" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O875" s="1" t="s">
         <v>407</v>
@@ -46085,7 +46218,7 @@
         <v>0</v>
       </c>
       <c r="N876" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O876" s="1" t="s">
         <v>408</v>
@@ -46135,7 +46268,7 @@
         <v>0</v>
       </c>
       <c r="N877" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O877" s="1" t="s">
         <v>409</v>
@@ -46185,7 +46318,7 @@
         <v>0</v>
       </c>
       <c r="N878" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O878" s="1" t="s">
         <v>410</v>
@@ -46235,7 +46368,7 @@
         <v>0</v>
       </c>
       <c r="N879" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O879" s="1" t="s">
         <v>420</v>
@@ -46285,7 +46418,7 @@
         <v>0</v>
       </c>
       <c r="N880" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O880" s="1" t="s">
         <v>426</v>
@@ -46335,7 +46468,7 @@
         <v>0</v>
       </c>
       <c r="N881" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O881" s="1" t="s">
         <v>426</v>
@@ -46385,7 +46518,7 @@
         <v>0</v>
       </c>
       <c r="N882" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O882" s="1" t="s">
         <v>426</v>
@@ -46435,7 +46568,7 @@
         <v>0</v>
       </c>
       <c r="N883" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O883" s="1" t="s">
         <v>426</v>
@@ -46485,7 +46618,7 @@
         <v>0</v>
       </c>
       <c r="N884" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O884" s="1" t="s">
         <v>426</v>
@@ -46535,7 +46668,7 @@
         <v>0</v>
       </c>
       <c r="N885" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O885" s="1" t="s">
         <v>426</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7557CA-2C7D-40CB-B883-EAF74E8947FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3870D5FE-AC14-4F82-BF7F-8FFD44AC7F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43915,7 +43915,7 @@
         <v>458</v>
       </c>
       <c r="K831" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L831" s="60">
         <v>30000</v>
@@ -43965,7 +43965,7 @@
         <v>459</v>
       </c>
       <c r="K832" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L832" s="60">
         <v>30000</v>
@@ -44015,7 +44015,7 @@
         <v>458</v>
       </c>
       <c r="K833" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L833" s="60">
         <v>30000</v>
@@ -44065,7 +44065,7 @@
         <v>458</v>
       </c>
       <c r="K834" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L834" s="60">
         <v>30000</v>
@@ -44115,7 +44115,7 @@
         <v>459</v>
       </c>
       <c r="K835" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L835" s="60">
         <v>30000</v>
@@ -44165,7 +44165,7 @@
         <v>459</v>
       </c>
       <c r="K836" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L836" s="60">
         <v>30000</v>
@@ -44215,7 +44215,7 @@
         <v>460</v>
       </c>
       <c r="K837" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L837" s="60">
         <v>30000</v>
@@ -44265,7 +44265,7 @@
         <v>459</v>
       </c>
       <c r="K838" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L838" s="60">
         <v>30000</v>
@@ -44315,7 +44315,7 @@
         <v>459</v>
       </c>
       <c r="K839" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L839" s="60">
         <v>30000</v>
@@ -44365,7 +44365,7 @@
         <v>461</v>
       </c>
       <c r="K840" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L840" s="60">
         <v>30000</v>
@@ -44415,7 +44415,7 @@
         <v>462</v>
       </c>
       <c r="K841" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L841" s="60">
         <v>30000</v>
@@ -44465,7 +44465,7 @@
         <v>463</v>
       </c>
       <c r="K842" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L842" s="60">
         <v>30000</v>
@@ -44515,7 +44515,7 @@
         <v>460</v>
       </c>
       <c r="K843" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L843" s="60">
         <v>30000</v>
@@ -44565,7 +44565,7 @@
         <v>464</v>
       </c>
       <c r="K844" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L844" s="60">
         <v>30000</v>
@@ -44615,7 +44615,7 @@
         <v>465</v>
       </c>
       <c r="K845" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L845" s="60">
         <v>30000</v>
@@ -44665,7 +44665,7 @@
         <v>466</v>
       </c>
       <c r="K846" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L846" s="60">
         <v>30000</v>
@@ -44715,7 +44715,7 @@
         <v>464</v>
       </c>
       <c r="K847" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L847" s="60">
         <v>30000</v>
@@ -44765,7 +44765,7 @@
         <v>465</v>
       </c>
       <c r="K848" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L848" s="60">
         <v>30000</v>
@@ -44815,7 +44815,7 @@
         <v>466</v>
       </c>
       <c r="K849" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L849" s="60">
         <v>30000</v>
@@ -44865,7 +44865,7 @@
         <v>464</v>
       </c>
       <c r="K850" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L850" s="60">
         <v>30000</v>
@@ -44915,7 +44915,7 @@
         <v>467</v>
       </c>
       <c r="K851" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L851" s="60">
         <v>30000</v>
@@ -44965,7 +44965,7 @@
         <v>464</v>
       </c>
       <c r="K852" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L852" s="60">
         <v>30000</v>
@@ -45015,7 +45015,7 @@
         <v>465</v>
       </c>
       <c r="K853" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L853" s="60">
         <v>30000</v>
@@ -45065,7 +45065,7 @@
         <v>466</v>
       </c>
       <c r="K854" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L854" s="60">
         <v>30000</v>
@@ -45115,7 +45115,7 @@
         <v>465</v>
       </c>
       <c r="K855" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L855" s="60">
         <v>30000</v>
@@ -45165,7 +45165,7 @@
         <v>468</v>
       </c>
       <c r="K856" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L856" s="60">
         <v>30000</v>
@@ -45215,7 +45215,7 @@
         <v>469</v>
       </c>
       <c r="K857" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L857" s="60">
         <v>30000</v>
@@ -45265,7 +45265,7 @@
         <v>470</v>
       </c>
       <c r="K858" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L858" s="60">
         <v>30000</v>
@@ -45315,7 +45315,7 @@
         <v>469</v>
       </c>
       <c r="K859" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L859" s="60">
         <v>30000</v>
@@ -45365,7 +45365,7 @@
         <v>470</v>
       </c>
       <c r="K860" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L860" s="60">
         <v>30000</v>
@@ -45415,7 +45415,7 @@
         <v>469</v>
       </c>
       <c r="K861" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L861" s="60">
         <v>30000</v>
@@ -45465,7 +45465,7 @@
         <v>469</v>
       </c>
       <c r="K862" s="60">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L862" s="60">
         <v>30000</v>
@@ -45515,7 +45515,7 @@
         <v>132</v>
       </c>
       <c r="K863" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L863" s="60">
         <v>30000</v>
@@ -45565,7 +45565,7 @@
         <v>132</v>
       </c>
       <c r="K864" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L864" s="60">
         <v>30000</v>
@@ -45615,7 +45615,7 @@
         <v>60</v>
       </c>
       <c r="K865" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L865" s="60">
         <v>30000</v>
@@ -45665,7 +45665,7 @@
         <v>132</v>
       </c>
       <c r="K866" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L866" s="60">
         <v>30000</v>
@@ -45715,7 +45715,7 @@
         <v>61</v>
       </c>
       <c r="K867" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L867" s="60">
         <v>30000</v>
@@ -45765,7 +45765,7 @@
         <v>133</v>
       </c>
       <c r="K868" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L868" s="60">
         <v>30000</v>
@@ -45815,7 +45815,7 @@
         <v>61</v>
       </c>
       <c r="K869" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L869" s="60">
         <v>30000</v>
@@ -45865,7 +45865,7 @@
         <v>61</v>
       </c>
       <c r="K870" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L870" s="60">
         <v>30000</v>
@@ -45915,7 +45915,7 @@
         <v>133</v>
       </c>
       <c r="K871" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L871" s="60">
         <v>30000</v>
@@ -45965,7 +45965,7 @@
         <v>61</v>
       </c>
       <c r="K872" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L872" s="60">
         <v>30000</v>
@@ -46015,7 +46015,7 @@
         <v>61</v>
       </c>
       <c r="K873" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L873" s="60">
         <v>30000</v>
@@ -46065,7 +46065,7 @@
         <v>61</v>
       </c>
       <c r="K874" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L874" s="60">
         <v>30000</v>
@@ -46115,7 +46115,7 @@
         <v>61</v>
       </c>
       <c r="K875" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L875" s="60">
         <v>30000</v>
@@ -46165,7 +46165,7 @@
         <v>61</v>
       </c>
       <c r="K876" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L876" s="60">
         <v>30000</v>
@@ -46215,7 +46215,7 @@
         <v>61</v>
       </c>
       <c r="K877" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L877" s="60">
         <v>30000</v>
@@ -46265,7 +46265,7 @@
         <v>61</v>
       </c>
       <c r="K878" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L878" s="60">
         <v>30000</v>
@@ -46315,7 +46315,7 @@
         <v>61</v>
       </c>
       <c r="K879" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L879" s="60">
         <v>30000</v>
@@ -46365,7 +46365,7 @@
         <v>61</v>
       </c>
       <c r="K880" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L880" s="60">
         <v>30000</v>
@@ -46415,7 +46415,7 @@
         <v>134</v>
       </c>
       <c r="K881" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L881" s="60">
         <v>30000</v>
@@ -46465,7 +46465,7 @@
         <v>134</v>
       </c>
       <c r="K882" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L882" s="60">
         <v>30000</v>
@@ -46515,7 +46515,7 @@
         <v>134</v>
       </c>
       <c r="K883" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L883" s="60">
         <v>30000</v>
@@ -46565,7 +46565,7 @@
         <v>63</v>
       </c>
       <c r="K884" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L884" s="60">
         <v>30000</v>
@@ -46615,7 +46615,7 @@
         <v>63</v>
       </c>
       <c r="K885" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L885" s="60">
         <v>30000</v>
@@ -46665,7 +46665,7 @@
         <v>63</v>
       </c>
       <c r="K886" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L886" s="60">
         <v>30000</v>
@@ -46715,7 +46715,7 @@
         <v>62</v>
       </c>
       <c r="K887" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L887" s="60">
         <v>30000</v>
@@ -46765,7 +46765,7 @@
         <v>63</v>
       </c>
       <c r="K888" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L888" s="60">
         <v>30000</v>
@@ -46815,7 +46815,7 @@
         <v>62</v>
       </c>
       <c r="K889" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L889" s="60">
         <v>30000</v>
@@ -46865,7 +46865,7 @@
         <v>63</v>
       </c>
       <c r="K890" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L890" s="60">
         <v>30000</v>
@@ -46915,7 +46915,7 @@
         <v>63</v>
       </c>
       <c r="K891" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L891" s="60">
         <v>30000</v>
@@ -46965,7 +46965,7 @@
         <v>62</v>
       </c>
       <c r="K892" s="60">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L892" s="60">
         <v>30000</v>
@@ -47014,8 +47014,8 @@
       <c r="J893" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K893" s="62">
-        <v>35</v>
+      <c r="K893" s="60">
+        <v>30</v>
       </c>
       <c r="L893" s="62">
         <v>30000</v>
@@ -47064,8 +47064,8 @@
       <c r="J894" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K894" s="62">
-        <v>35</v>
+      <c r="K894" s="60">
+        <v>30</v>
       </c>
       <c r="L894" s="62">
         <v>30000</v>
@@ -47114,8 +47114,8 @@
       <c r="J895" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K895" s="62">
-        <v>35</v>
+      <c r="K895" s="60">
+        <v>30</v>
       </c>
       <c r="L895" s="62">
         <v>30000</v>
@@ -47164,8 +47164,8 @@
       <c r="J896" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K896" s="62">
-        <v>35</v>
+      <c r="K896" s="60">
+        <v>30</v>
       </c>
       <c r="L896" s="62">
         <v>30000</v>
@@ -47214,8 +47214,8 @@
       <c r="J897" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K897" s="62">
-        <v>35</v>
+      <c r="K897" s="60">
+        <v>30</v>
       </c>
       <c r="L897" s="62">
         <v>30000</v>
@@ -47264,8 +47264,8 @@
       <c r="J898" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K898" s="62">
-        <v>35</v>
+      <c r="K898" s="60">
+        <v>30</v>
       </c>
       <c r="L898" s="62">
         <v>30000</v>
@@ -47314,8 +47314,8 @@
       <c r="J899" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K899" s="62">
-        <v>35</v>
+      <c r="K899" s="60">
+        <v>30</v>
       </c>
       <c r="L899" s="62">
         <v>30000</v>
@@ -47364,8 +47364,8 @@
       <c r="J900" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K900" s="62">
-        <v>35</v>
+      <c r="K900" s="60">
+        <v>30</v>
       </c>
       <c r="L900" s="62">
         <v>30000</v>
@@ -47414,8 +47414,8 @@
       <c r="J901" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K901" s="62">
-        <v>35</v>
+      <c r="K901" s="60">
+        <v>30</v>
       </c>
       <c r="L901" s="62">
         <v>30000</v>
@@ -47464,8 +47464,8 @@
       <c r="J902" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K902" s="62">
-        <v>35</v>
+      <c r="K902" s="60">
+        <v>30</v>
       </c>
       <c r="L902" s="62">
         <v>30000</v>
@@ -47514,8 +47514,8 @@
       <c r="J903" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K903" s="62">
-        <v>35</v>
+      <c r="K903" s="60">
+        <v>30</v>
       </c>
       <c r="L903" s="62">
         <v>30000</v>
@@ -47564,8 +47564,8 @@
       <c r="J904" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K904" s="62">
-        <v>35</v>
+      <c r="K904" s="60">
+        <v>30</v>
       </c>
       <c r="L904" s="62">
         <v>30000</v>
@@ -47614,8 +47614,8 @@
       <c r="J905" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K905" s="62">
-        <v>35</v>
+      <c r="K905" s="60">
+        <v>30</v>
       </c>
       <c r="L905" s="62">
         <v>30000</v>
@@ -47664,8 +47664,8 @@
       <c r="J906" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K906" s="62">
-        <v>35</v>
+      <c r="K906" s="60">
+        <v>30</v>
       </c>
       <c r="L906" s="62">
         <v>30000</v>
@@ -47714,8 +47714,8 @@
       <c r="J907" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K907" s="62">
-        <v>35</v>
+      <c r="K907" s="60">
+        <v>30</v>
       </c>
       <c r="L907" s="62">
         <v>30000</v>
@@ -47764,8 +47764,8 @@
       <c r="J908" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K908" s="62">
-        <v>35</v>
+      <c r="K908" s="60">
+        <v>30</v>
       </c>
       <c r="L908" s="62">
         <v>30000</v>
@@ -47814,8 +47814,8 @@
       <c r="J909" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K909" s="62">
-        <v>35</v>
+      <c r="K909" s="60">
+        <v>30</v>
       </c>
       <c r="L909" s="62">
         <v>30000</v>
@@ -47864,8 +47864,8 @@
       <c r="J910" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K910" s="62">
-        <v>35</v>
+      <c r="K910" s="60">
+        <v>30</v>
       </c>
       <c r="L910" s="62">
         <v>30000</v>
@@ -47914,8 +47914,8 @@
       <c r="J911" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K911" s="62">
-        <v>35</v>
+      <c r="K911" s="60">
+        <v>30</v>
       </c>
       <c r="L911" s="62">
         <v>30000</v>
@@ -47964,8 +47964,8 @@
       <c r="J912" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K912" s="62">
-        <v>35</v>
+      <c r="K912" s="60">
+        <v>30</v>
       </c>
       <c r="L912" s="62">
         <v>30000</v>
@@ -48014,8 +48014,8 @@
       <c r="J913" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K913" s="62">
-        <v>35</v>
+      <c r="K913" s="60">
+        <v>30</v>
       </c>
       <c r="L913" s="62">
         <v>30000</v>
@@ -48064,8 +48064,8 @@
       <c r="J914" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K914" s="62">
-        <v>35</v>
+      <c r="K914" s="60">
+        <v>30</v>
       </c>
       <c r="L914" s="62">
         <v>30000</v>
@@ -48114,8 +48114,8 @@
       <c r="J915" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K915" s="62">
-        <v>35</v>
+      <c r="K915" s="60">
+        <v>30</v>
       </c>
       <c r="L915" s="62">
         <v>30000</v>
@@ -48164,8 +48164,8 @@
       <c r="J916" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K916" s="62">
-        <v>35</v>
+      <c r="K916" s="60">
+        <v>30</v>
       </c>
       <c r="L916" s="62">
         <v>30000</v>
@@ -48214,8 +48214,8 @@
       <c r="J917" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K917" s="62">
-        <v>35</v>
+      <c r="K917" s="60">
+        <v>30</v>
       </c>
       <c r="L917" s="62">
         <v>30000</v>
@@ -48264,8 +48264,8 @@
       <c r="J918" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K918" s="62">
-        <v>35</v>
+      <c r="K918" s="60">
+        <v>30</v>
       </c>
       <c r="L918" s="62">
         <v>30000</v>
@@ -48314,8 +48314,8 @@
       <c r="J919" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K919" s="62">
-        <v>35</v>
+      <c r="K919" s="60">
+        <v>30</v>
       </c>
       <c r="L919" s="62">
         <v>30000</v>
@@ -48364,8 +48364,8 @@
       <c r="J920" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K920" s="62">
-        <v>35</v>
+      <c r="K920" s="60">
+        <v>30</v>
       </c>
       <c r="L920" s="62">
         <v>30000</v>
@@ -48414,8 +48414,8 @@
       <c r="J921" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K921" s="62">
-        <v>35</v>
+      <c r="K921" s="60">
+        <v>30</v>
       </c>
       <c r="L921" s="62">
         <v>30000</v>
@@ -48464,8 +48464,8 @@
       <c r="J922" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K922" s="62">
-        <v>35</v>
+      <c r="K922" s="60">
+        <v>30</v>
       </c>
       <c r="L922" s="62">
         <v>30000</v>
@@ -48514,8 +48514,8 @@
       <c r="J923" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K923" s="62">
-        <v>35</v>
+      <c r="K923" s="60">
+        <v>30</v>
       </c>
       <c r="L923" s="62">
         <v>30000</v>
@@ -48564,8 +48564,8 @@
       <c r="J924" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K924" s="62">
-        <v>35</v>
+      <c r="K924" s="60">
+        <v>30</v>
       </c>
       <c r="L924" s="62">
         <v>30000</v>
@@ -48614,8 +48614,8 @@
       <c r="J925" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="K925" s="62">
-        <v>35</v>
+      <c r="K925" s="60">
+        <v>30</v>
       </c>
       <c r="L925" s="62">
         <v>30000</v>
@@ -48664,8 +48664,8 @@
       <c r="J926" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K926" s="62">
-        <v>35</v>
+      <c r="K926" s="60">
+        <v>30</v>
       </c>
       <c r="L926" s="62">
         <v>30000</v>
@@ -48714,8 +48714,8 @@
       <c r="J927" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K927" s="62">
-        <v>35</v>
+      <c r="K927" s="60">
+        <v>30</v>
       </c>
       <c r="L927" s="62">
         <v>30000</v>
@@ -48764,8 +48764,8 @@
       <c r="J928" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K928" s="62">
-        <v>35</v>
+      <c r="K928" s="60">
+        <v>30</v>
       </c>
       <c r="L928" s="62">
         <v>30000</v>
@@ -48814,8 +48814,8 @@
       <c r="J929" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K929" s="62">
-        <v>35</v>
+      <c r="K929" s="60">
+        <v>30</v>
       </c>
       <c r="L929" s="62">
         <v>30000</v>
@@ -48864,8 +48864,8 @@
       <c r="J930" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K930" s="62">
-        <v>35</v>
+      <c r="K930" s="60">
+        <v>30</v>
       </c>
       <c r="L930" s="62">
         <v>30000</v>
@@ -48914,8 +48914,8 @@
       <c r="J931" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K931" s="62">
-        <v>35</v>
+      <c r="K931" s="60">
+        <v>30</v>
       </c>
       <c r="L931" s="62">
         <v>30000</v>
@@ -48964,8 +48964,8 @@
       <c r="J932" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K932" s="62">
-        <v>35</v>
+      <c r="K932" s="60">
+        <v>30</v>
       </c>
       <c r="L932" s="62">
         <v>30000</v>
@@ -49014,8 +49014,8 @@
       <c r="J933" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K933" s="62">
-        <v>35</v>
+      <c r="K933" s="60">
+        <v>30</v>
       </c>
       <c r="L933" s="62">
         <v>30000</v>
@@ -49064,8 +49064,8 @@
       <c r="J934" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K934" s="62">
-        <v>35</v>
+      <c r="K934" s="60">
+        <v>30</v>
       </c>
       <c r="L934" s="62">
         <v>30000</v>
@@ -49114,8 +49114,8 @@
       <c r="J935" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K935" s="62">
-        <v>35</v>
+      <c r="K935" s="60">
+        <v>30</v>
       </c>
       <c r="L935" s="62">
         <v>30000</v>
@@ -49164,8 +49164,8 @@
       <c r="J936" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K936" s="62">
-        <v>35</v>
+      <c r="K936" s="60">
+        <v>30</v>
       </c>
       <c r="L936" s="62">
         <v>30000</v>
@@ -49214,8 +49214,8 @@
       <c r="J937" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K937" s="62">
-        <v>35</v>
+      <c r="K937" s="60">
+        <v>30</v>
       </c>
       <c r="L937" s="62">
         <v>30000</v>
@@ -49264,8 +49264,8 @@
       <c r="J938" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K938" s="62">
-        <v>35</v>
+      <c r="K938" s="60">
+        <v>30</v>
       </c>
       <c r="L938" s="62">
         <v>30000</v>
@@ -49314,8 +49314,8 @@
       <c r="J939" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="K939" s="62">
-        <v>35</v>
+      <c r="K939" s="60">
+        <v>30</v>
       </c>
       <c r="L939" s="62">
         <v>30000</v>
@@ -49364,8 +49364,8 @@
       <c r="J940" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="K940" s="65">
-        <v>35</v>
+      <c r="K940" s="60">
+        <v>30</v>
       </c>
       <c r="L940" s="65">
         <v>30000</v>
@@ -49415,7 +49415,7 @@
         <v>135</v>
       </c>
       <c r="K941" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L941" s="62">
         <v>30000</v>
@@ -49465,7 +49465,7 @@
         <v>135</v>
       </c>
       <c r="K942" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L942" s="62">
         <v>30000</v>
@@ -49515,7 +49515,7 @@
         <v>135</v>
       </c>
       <c r="K943" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L943" s="62">
         <v>30000</v>
@@ -49565,7 +49565,7 @@
         <v>135</v>
       </c>
       <c r="K944" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L944" s="62">
         <v>30000</v>
@@ -49615,7 +49615,7 @@
         <v>136</v>
       </c>
       <c r="K945" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L945" s="62">
         <v>30000</v>
@@ -49665,7 +49665,7 @@
         <v>136</v>
       </c>
       <c r="K946" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L946" s="62">
         <v>30000</v>
@@ -49715,7 +49715,7 @@
         <v>136</v>
       </c>
       <c r="K947" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L947" s="62">
         <v>30000</v>
@@ -49765,7 +49765,7 @@
         <v>136</v>
       </c>
       <c r="K948" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L948" s="62">
         <v>30000</v>
@@ -49815,7 +49815,7 @@
         <v>56</v>
       </c>
       <c r="K949" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L949" s="62">
         <v>30000</v>
@@ -49865,7 +49865,7 @@
         <v>136</v>
       </c>
       <c r="K950" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L950" s="62">
         <v>30000</v>
@@ -49915,7 +49915,7 @@
         <v>56</v>
       </c>
       <c r="K951" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L951" s="62">
         <v>30000</v>
@@ -49965,7 +49965,7 @@
         <v>136</v>
       </c>
       <c r="K952" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L952" s="62">
         <v>30000</v>
@@ -50015,7 +50015,7 @@
         <v>136</v>
       </c>
       <c r="K953" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L953" s="62">
         <v>30000</v>
@@ -50065,7 +50065,7 @@
         <v>136</v>
       </c>
       <c r="K954" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L954" s="62">
         <v>30000</v>
@@ -50115,7 +50115,7 @@
         <v>136</v>
       </c>
       <c r="K955" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L955" s="62">
         <v>30000</v>
@@ -50165,7 +50165,7 @@
         <v>136</v>
       </c>
       <c r="K956" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L956" s="62">
         <v>30000</v>
@@ -50215,7 +50215,7 @@
         <v>136</v>
       </c>
       <c r="K957" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L957" s="62">
         <v>30000</v>
@@ -50265,7 +50265,7 @@
         <v>56</v>
       </c>
       <c r="K958" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L958" s="62">
         <v>30000</v>
@@ -50314,8 +50314,8 @@
       <c r="J959" s="68" t="s">
         <v>136</v>
       </c>
-      <c r="K959" s="67">
-        <v>100</v>
+      <c r="K959" s="62">
+        <v>200</v>
       </c>
       <c r="L959" s="67">
         <v>30000</v>
@@ -50365,7 +50365,7 @@
         <v>57</v>
       </c>
       <c r="K960" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L960" s="62">
         <v>30000</v>
@@ -50415,7 +50415,7 @@
         <v>57</v>
       </c>
       <c r="K961" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L961" s="62">
         <v>30000</v>
@@ -50465,7 +50465,7 @@
         <v>57</v>
       </c>
       <c r="K962" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L962" s="62">
         <v>30000</v>
@@ -50515,7 +50515,7 @@
         <v>58</v>
       </c>
       <c r="K963" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L963" s="62">
         <v>30000</v>
@@ -50565,7 +50565,7 @@
         <v>58</v>
       </c>
       <c r="K964" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L964" s="62">
         <v>30000</v>
@@ -50615,7 +50615,7 @@
         <v>58</v>
       </c>
       <c r="K965" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L965" s="62">
         <v>30000</v>
@@ -50664,8 +50664,8 @@
       <c r="J966" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="K966" s="69">
-        <v>100</v>
+      <c r="K966" s="62">
+        <v>200</v>
       </c>
       <c r="L966" s="69">
         <v>30000</v>
@@ -50715,7 +50715,7 @@
         <v>58</v>
       </c>
       <c r="K967" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L967" s="62">
         <v>30000</v>
@@ -50765,7 +50765,7 @@
         <v>58</v>
       </c>
       <c r="K968" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L968" s="62">
         <v>30000</v>
@@ -50815,7 +50815,7 @@
         <v>58</v>
       </c>
       <c r="K969" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L969" s="62">
         <v>30000</v>
@@ -50865,7 +50865,7 @@
         <v>58</v>
       </c>
       <c r="K970" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L970" s="62">
         <v>30000</v>
@@ -50915,7 +50915,7 @@
         <v>137</v>
       </c>
       <c r="K971" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L971" s="62">
         <v>30000</v>
@@ -50965,7 +50965,7 @@
         <v>58</v>
       </c>
       <c r="K972" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L972" s="62">
         <v>30000</v>
@@ -51015,7 +51015,7 @@
         <v>58</v>
       </c>
       <c r="K973" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L973" s="62">
         <v>30000</v>
@@ -51065,7 +51065,7 @@
         <v>58</v>
       </c>
       <c r="K974" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L974" s="62">
         <v>30000</v>
@@ -51114,8 +51114,8 @@
       <c r="J975" s="70" t="s">
         <v>137</v>
       </c>
-      <c r="K975" s="69">
-        <v>100</v>
+      <c r="K975" s="62">
+        <v>200</v>
       </c>
       <c r="L975" s="69">
         <v>30000</v>
@@ -51165,7 +51165,7 @@
         <v>58</v>
       </c>
       <c r="K976" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L976" s="62">
         <v>30000</v>
@@ -51215,7 +51215,7 @@
         <v>58</v>
       </c>
       <c r="K977" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L977" s="62">
         <v>30000</v>
@@ -51265,7 +51265,7 @@
         <v>58</v>
       </c>
       <c r="K978" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L978" s="62">
         <v>30000</v>
@@ -51315,7 +51315,7 @@
         <v>58</v>
       </c>
       <c r="K979" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L979" s="62">
         <v>30000</v>
@@ -51365,7 +51365,7 @@
         <v>58</v>
       </c>
       <c r="K980" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L980" s="62">
         <v>30000</v>
@@ -51415,7 +51415,7 @@
         <v>58</v>
       </c>
       <c r="K981" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L981" s="62">
         <v>30000</v>
@@ -51465,7 +51465,7 @@
         <v>59</v>
       </c>
       <c r="K982" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L982" s="62">
         <v>30000</v>
@@ -51515,7 +51515,7 @@
         <v>58</v>
       </c>
       <c r="K983" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L983" s="62">
         <v>30000</v>
@@ -51565,7 +51565,7 @@
         <v>58</v>
       </c>
       <c r="K984" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L984" s="62">
         <v>30000</v>
@@ -51614,8 +51614,8 @@
       <c r="J985" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="K985" s="69">
-        <v>100</v>
+      <c r="K985" s="62">
+        <v>200</v>
       </c>
       <c r="L985" s="69">
         <v>30000</v>
@@ -51665,7 +51665,7 @@
         <v>58</v>
       </c>
       <c r="K986" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L986" s="62">
         <v>30000</v>
@@ -51715,7 +51715,7 @@
         <v>58</v>
       </c>
       <c r="K987" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L987" s="62">
         <v>30000</v>
@@ -51765,7 +51765,7 @@
         <v>59</v>
       </c>
       <c r="K988" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L988" s="62">
         <v>30000</v>
@@ -51815,7 +51815,7 @@
         <v>58</v>
       </c>
       <c r="K989" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L989" s="62">
         <v>30000</v>
@@ -51865,7 +51865,7 @@
         <v>58</v>
       </c>
       <c r="K990" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L990" s="62">
         <v>30000</v>
@@ -51915,7 +51915,7 @@
         <v>59</v>
       </c>
       <c r="K991" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L991" s="62">
         <v>30000</v>
@@ -51965,7 +51965,7 @@
         <v>58</v>
       </c>
       <c r="K992" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L992" s="62">
         <v>30000</v>
@@ -52015,7 +52015,7 @@
         <v>59</v>
       </c>
       <c r="K993" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L993" s="62">
         <v>30000</v>
@@ -52065,7 +52065,7 @@
         <v>58</v>
       </c>
       <c r="K994" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L994" s="62">
         <v>30000</v>
@@ -52115,7 +52115,7 @@
         <v>59</v>
       </c>
       <c r="K995" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L995" s="62">
         <v>30000</v>
@@ -52164,8 +52164,8 @@
       <c r="J996" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="K996" s="69">
-        <v>100</v>
+      <c r="K996" s="62">
+        <v>200</v>
       </c>
       <c r="L996" s="69">
         <v>30000</v>
@@ -52215,7 +52215,7 @@
         <v>58</v>
       </c>
       <c r="K997" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L997" s="62">
         <v>30000</v>
@@ -52265,7 +52265,7 @@
         <v>59</v>
       </c>
       <c r="K998" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L998" s="62">
         <v>30000</v>
@@ -52315,7 +52315,7 @@
         <v>59</v>
       </c>
       <c r="K999" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L999" s="62">
         <v>30000</v>
@@ -52365,7 +52365,7 @@
         <v>58</v>
       </c>
       <c r="K1000" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1000" s="62">
         <v>30000</v>
@@ -52415,7 +52415,7 @@
         <v>59</v>
       </c>
       <c r="K1001" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1001" s="62">
         <v>30000</v>
@@ -52465,7 +52465,7 @@
         <v>59</v>
       </c>
       <c r="K1002" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1002" s="62">
         <v>30000</v>
@@ -52515,7 +52515,7 @@
         <v>59</v>
       </c>
       <c r="K1003" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1003" s="62">
         <v>30000</v>
@@ -52565,7 +52565,7 @@
         <v>58</v>
       </c>
       <c r="K1004" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1004" s="62">
         <v>30000</v>
@@ -52615,7 +52615,7 @@
         <v>59</v>
       </c>
       <c r="K1005" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1005" s="62">
         <v>30000</v>
@@ -52665,7 +52665,7 @@
         <v>59</v>
       </c>
       <c r="K1006" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1006" s="62">
         <v>30000</v>
@@ -52715,7 +52715,7 @@
         <v>59</v>
       </c>
       <c r="K1007" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1007" s="62">
         <v>30000</v>
@@ -52764,8 +52764,8 @@
       <c r="J1008" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="K1008" s="69">
-        <v>100</v>
+      <c r="K1008" s="62">
+        <v>200</v>
       </c>
       <c r="L1008" s="69">
         <v>30000</v>
@@ -52815,7 +52815,7 @@
         <v>59</v>
       </c>
       <c r="K1009" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1009" s="62">
         <v>30000</v>
@@ -52865,7 +52865,7 @@
         <v>59</v>
       </c>
       <c r="K1010" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1010" s="62">
         <v>30000</v>
@@ -52915,7 +52915,7 @@
         <v>59</v>
       </c>
       <c r="K1011" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1011" s="62">
         <v>30000</v>
@@ -52965,7 +52965,7 @@
         <v>59</v>
       </c>
       <c r="K1012" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1012" s="62">
         <v>30000</v>
@@ -53015,7 +53015,7 @@
         <v>59</v>
       </c>
       <c r="K1013" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1013" s="62">
         <v>30000</v>
@@ -53065,7 +53065,7 @@
         <v>59</v>
       </c>
       <c r="K1014" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1014" s="62">
         <v>30000</v>
@@ -53115,7 +53115,7 @@
         <v>59</v>
       </c>
       <c r="K1015" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1015" s="62">
         <v>30000</v>
@@ -53165,7 +53165,7 @@
         <v>59</v>
       </c>
       <c r="K1016" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1016" s="62">
         <v>30000</v>
@@ -53215,7 +53215,7 @@
         <v>59</v>
       </c>
       <c r="K1017" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1017" s="62">
         <v>30000</v>
@@ -53265,7 +53265,7 @@
         <v>59</v>
       </c>
       <c r="K1018" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1018" s="62">
         <v>30000</v>
@@ -53315,7 +53315,7 @@
         <v>59</v>
       </c>
       <c r="K1019" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1019" s="62">
         <v>30000</v>
@@ -53365,7 +53365,7 @@
         <v>59</v>
       </c>
       <c r="K1020" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1020" s="62">
         <v>30000</v>
@@ -53415,7 +53415,7 @@
         <v>59</v>
       </c>
       <c r="K1021" s="62">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L1021" s="62">
         <v>30000</v>
@@ -53465,7 +53465,7 @@
         <v>138</v>
       </c>
       <c r="K1022" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1022" s="62">
         <v>30000</v>
@@ -53515,7 +53515,7 @@
         <v>138</v>
       </c>
       <c r="K1023" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1023" s="62">
         <v>30000</v>
@@ -53565,7 +53565,7 @@
         <v>138</v>
       </c>
       <c r="K1024" s="71">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1024" s="71">
         <v>30000</v>
@@ -53615,7 +53615,7 @@
         <v>139</v>
       </c>
       <c r="K1025" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1025" s="62">
         <v>30000</v>
@@ -53665,7 +53665,7 @@
         <v>139</v>
       </c>
       <c r="K1026" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1026" s="62">
         <v>30000</v>
@@ -53715,7 +53715,7 @@
         <v>139</v>
       </c>
       <c r="K1027" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1027" s="62">
         <v>30000</v>
@@ -53765,7 +53765,7 @@
         <v>139</v>
       </c>
       <c r="K1028" s="69">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1028" s="69">
         <v>30000</v>
@@ -53815,7 +53815,7 @@
         <v>139</v>
       </c>
       <c r="K1029" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1029" s="62">
         <v>30000</v>
@@ -53865,7 +53865,7 @@
         <v>139</v>
       </c>
       <c r="K1030" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1030" s="62">
         <v>30000</v>
@@ -53915,7 +53915,7 @@
         <v>139</v>
       </c>
       <c r="K1031" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1031" s="62">
         <v>30000</v>
@@ -53965,7 +53965,7 @@
         <v>139</v>
       </c>
       <c r="K1032" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1032" s="62">
         <v>30000</v>
@@ -54015,7 +54015,7 @@
         <v>140</v>
       </c>
       <c r="K1033" s="69">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1033" s="69">
         <v>30000</v>
@@ -54065,7 +54065,7 @@
         <v>139</v>
       </c>
       <c r="K1034" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1034" s="62">
         <v>30000</v>
@@ -54115,7 +54115,7 @@
         <v>139</v>
       </c>
       <c r="K1035" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1035" s="62">
         <v>30000</v>
@@ -54165,7 +54165,7 @@
         <v>139</v>
       </c>
       <c r="K1036" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1036" s="62">
         <v>30000</v>
@@ -54215,7 +54215,7 @@
         <v>139</v>
       </c>
       <c r="K1037" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1037" s="62">
         <v>30000</v>
@@ -54265,7 +54265,7 @@
         <v>139</v>
       </c>
       <c r="K1038" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1038" s="62">
         <v>30000</v>
@@ -54315,7 +54315,7 @@
         <v>139</v>
       </c>
       <c r="K1039" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1039" s="62">
         <v>30000</v>
@@ -54365,7 +54365,7 @@
         <v>139</v>
       </c>
       <c r="K1040" s="67">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1040" s="67">
         <v>30000</v>
@@ -54415,7 +54415,7 @@
         <v>141</v>
       </c>
       <c r="K1041" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1041" s="62">
         <v>30000</v>
@@ -54465,7 +54465,7 @@
         <v>141</v>
       </c>
       <c r="K1042" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1042" s="62">
         <v>30000</v>
@@ -54515,7 +54515,7 @@
         <v>141</v>
       </c>
       <c r="K1043" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1043" s="62">
         <v>30000</v>
@@ -54565,7 +54565,7 @@
         <v>141</v>
       </c>
       <c r="K1044" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1044" s="62">
         <v>30000</v>
@@ -54615,7 +54615,7 @@
         <v>141</v>
       </c>
       <c r="K1045" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1045" s="62">
         <v>30000</v>
@@ -54665,7 +54665,7 @@
         <v>142</v>
       </c>
       <c r="K1046" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1046" s="62">
         <v>30000</v>
@@ -54715,7 +54715,7 @@
         <v>142</v>
       </c>
       <c r="K1047" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1047" s="62">
         <v>30000</v>
@@ -54765,7 +54765,7 @@
         <v>142</v>
       </c>
       <c r="K1048" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1048" s="62">
         <v>30000</v>
@@ -54815,7 +54815,7 @@
         <v>142</v>
       </c>
       <c r="K1049" s="69">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1049" s="69">
         <v>30000</v>
@@ -54865,7 +54865,7 @@
         <v>142</v>
       </c>
       <c r="K1050" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1050" s="62">
         <v>30000</v>
@@ -54915,7 +54915,7 @@
         <v>143</v>
       </c>
       <c r="K1051" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1051" s="62">
         <v>30000</v>
@@ -54965,7 +54965,7 @@
         <v>142</v>
       </c>
       <c r="K1052" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1052" s="62">
         <v>30000</v>
@@ -55015,7 +55015,7 @@
         <v>142</v>
       </c>
       <c r="K1053" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1053" s="62">
         <v>30000</v>
@@ -55065,7 +55065,7 @@
         <v>143</v>
       </c>
       <c r="K1054" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1054" s="62">
         <v>30000</v>
@@ -55115,7 +55115,7 @@
         <v>142</v>
       </c>
       <c r="K1055" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1055" s="62">
         <v>30000</v>
@@ -55165,7 +55165,7 @@
         <v>142</v>
       </c>
       <c r="K1056" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1056" s="62">
         <v>30000</v>
@@ -55215,7 +55215,7 @@
         <v>143</v>
       </c>
       <c r="K1057" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1057" s="62">
         <v>30000</v>
@@ -55265,7 +55265,7 @@
         <v>142</v>
       </c>
       <c r="K1058" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1058" s="62">
         <v>30000</v>
@@ -55315,7 +55315,7 @@
         <v>143</v>
       </c>
       <c r="K1059" s="69">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1059" s="69">
         <v>30000</v>
@@ -55365,7 +55365,7 @@
         <v>142</v>
       </c>
       <c r="K1060" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1060" s="62">
         <v>30000</v>
@@ -55415,7 +55415,7 @@
         <v>142</v>
       </c>
       <c r="K1061" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1061" s="62">
         <v>30000</v>
@@ -55465,7 +55465,7 @@
         <v>143</v>
       </c>
       <c r="K1062" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1062" s="62">
         <v>30000</v>
@@ -55515,7 +55515,7 @@
         <v>142</v>
       </c>
       <c r="K1063" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1063" s="62">
         <v>30000</v>
@@ -55565,7 +55565,7 @@
         <v>142</v>
       </c>
       <c r="K1064" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1064" s="62">
         <v>30000</v>
@@ -55615,7 +55615,7 @@
         <v>143</v>
       </c>
       <c r="K1065" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1065" s="62">
         <v>30000</v>
@@ -55665,7 +55665,7 @@
         <v>142</v>
       </c>
       <c r="K1066" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1066" s="62">
         <v>30000</v>
@@ -55715,7 +55715,7 @@
         <v>142</v>
       </c>
       <c r="K1067" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1067" s="62">
         <v>30000</v>
@@ -55765,7 +55765,7 @@
         <v>143</v>
       </c>
       <c r="K1068" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1068" s="62">
         <v>30000</v>
@@ -55815,7 +55815,7 @@
         <v>142</v>
       </c>
       <c r="K1069" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1069" s="62">
         <v>30000</v>
@@ -55865,7 +55865,7 @@
         <v>143</v>
       </c>
       <c r="K1070" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1070" s="62">
         <v>30000</v>
@@ -55915,7 +55915,7 @@
         <v>142</v>
       </c>
       <c r="K1071" s="69">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1071" s="69">
         <v>30000</v>
@@ -55965,7 +55965,7 @@
         <v>142</v>
       </c>
       <c r="K1072" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1072" s="62">
         <v>30000</v>
@@ -56015,7 +56015,7 @@
         <v>143</v>
       </c>
       <c r="K1073" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1073" s="62">
         <v>30000</v>
@@ -56065,7 +56065,7 @@
         <v>143</v>
       </c>
       <c r="K1074" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1074" s="62">
         <v>30000</v>
@@ -56115,7 +56115,7 @@
         <v>142</v>
       </c>
       <c r="K1075" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1075" s="62">
         <v>30000</v>
@@ -56165,7 +56165,7 @@
         <v>142</v>
       </c>
       <c r="K1076" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1076" s="62">
         <v>30000</v>
@@ -56215,7 +56215,7 @@
         <v>143</v>
       </c>
       <c r="K1077" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1077" s="62">
         <v>30000</v>
@@ -56265,7 +56265,7 @@
         <v>143</v>
       </c>
       <c r="K1078" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1078" s="62">
         <v>30000</v>
@@ -56315,7 +56315,7 @@
         <v>142</v>
       </c>
       <c r="K1079" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1079" s="62">
         <v>30000</v>
@@ -56365,7 +56365,7 @@
         <v>143</v>
       </c>
       <c r="K1080" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1080" s="62">
         <v>30000</v>
@@ -56415,7 +56415,7 @@
         <v>143</v>
       </c>
       <c r="K1081" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1081" s="62">
         <v>30000</v>
@@ -56465,7 +56465,7 @@
         <v>142</v>
       </c>
       <c r="K1082" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1082" s="62">
         <v>30000</v>
@@ -56515,7 +56515,7 @@
         <v>143</v>
       </c>
       <c r="K1083" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1083" s="62">
         <v>30000</v>
@@ -56565,7 +56565,7 @@
         <v>143</v>
       </c>
       <c r="K1084" s="69">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1084" s="69">
         <v>30000</v>
@@ -56615,7 +56615,7 @@
         <v>143</v>
       </c>
       <c r="K1085" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1085" s="62">
         <v>30000</v>
@@ -56665,7 +56665,7 @@
         <v>143</v>
       </c>
       <c r="K1086" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1086" s="62">
         <v>30000</v>
@@ -56715,7 +56715,7 @@
         <v>143</v>
       </c>
       <c r="K1087" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1087" s="62">
         <v>30000</v>
@@ -56765,7 +56765,7 @@
         <v>143</v>
       </c>
       <c r="K1088" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1088" s="62">
         <v>30000</v>
@@ -56815,7 +56815,7 @@
         <v>143</v>
       </c>
       <c r="K1089" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1089" s="62">
         <v>30000</v>
@@ -56865,7 +56865,7 @@
         <v>143</v>
       </c>
       <c r="K1090" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1090" s="62">
         <v>30000</v>
@@ -56915,7 +56915,7 @@
         <v>143</v>
       </c>
       <c r="K1091" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1091" s="62">
         <v>30000</v>
@@ -56965,7 +56965,7 @@
         <v>143</v>
       </c>
       <c r="K1092" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1092" s="62">
         <v>30000</v>
@@ -57015,7 +57015,7 @@
         <v>143</v>
       </c>
       <c r="K1093" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1093" s="62">
         <v>30000</v>
@@ -57065,7 +57065,7 @@
         <v>143</v>
       </c>
       <c r="K1094" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1094" s="62">
         <v>30000</v>
@@ -57115,7 +57115,7 @@
         <v>143</v>
       </c>
       <c r="K1095" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1095" s="62">
         <v>30000</v>
@@ -57165,7 +57165,7 @@
         <v>143</v>
       </c>
       <c r="K1096" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1096" s="62">
         <v>30000</v>
@@ -57215,7 +57215,7 @@
         <v>143</v>
       </c>
       <c r="K1097" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1097" s="62">
         <v>30000</v>
@@ -57265,7 +57265,7 @@
         <v>143</v>
       </c>
       <c r="K1098" s="69">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1098" s="69">
         <v>30000</v>
@@ -57315,7 +57315,7 @@
         <v>143</v>
       </c>
       <c r="K1099" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1099" s="62">
         <v>30000</v>
@@ -57365,7 +57365,7 @@
         <v>144</v>
       </c>
       <c r="K1100" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1100" s="62">
         <v>30000</v>
@@ -57415,7 +57415,7 @@
         <v>144</v>
       </c>
       <c r="K1101" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1101" s="62">
         <v>30000</v>
@@ -57465,7 +57465,7 @@
         <v>144</v>
       </c>
       <c r="K1102" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1102" s="62">
         <v>30000</v>
@@ -57515,7 +57515,7 @@
         <v>144</v>
       </c>
       <c r="K1103" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1103" s="62">
         <v>30000</v>
@@ -57565,7 +57565,7 @@
         <v>144</v>
       </c>
       <c r="K1104" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1104" s="62">
         <v>30000</v>
@@ -57615,7 +57615,7 @@
         <v>144</v>
       </c>
       <c r="K1105" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1105" s="62">
         <v>30000</v>
@@ -57665,7 +57665,7 @@
         <v>143</v>
       </c>
       <c r="K1106" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1106" s="62">
         <v>30000</v>
@@ -57715,7 +57715,7 @@
         <v>144</v>
       </c>
       <c r="K1107" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1107" s="62">
         <v>30000</v>
@@ -57765,7 +57765,7 @@
         <v>144</v>
       </c>
       <c r="K1108" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1108" s="62">
         <v>30000</v>
@@ -57815,7 +57815,7 @@
         <v>144</v>
       </c>
       <c r="K1109" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1109" s="62">
         <v>30000</v>
@@ -57865,7 +57865,7 @@
         <v>144</v>
       </c>
       <c r="K1110" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1110" s="62">
         <v>30000</v>
@@ -57915,7 +57915,7 @@
         <v>144</v>
       </c>
       <c r="K1111" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1111" s="62">
         <v>30000</v>
@@ -57965,7 +57965,7 @@
         <v>144</v>
       </c>
       <c r="K1112" s="62">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="L1112" s="62">
         <v>30000</v>
@@ -57985,14 +57985,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A1112">
+    <cfRule type="duplicateValues" dxfId="3" priority="24"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A5:A53">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54:A96 A98:A102">
-    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A1112">
-    <cfRule type="duplicateValues" dxfId="1" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A169:A331 A333:A892">
     <cfRule type="duplicateValues" dxfId="0" priority="26"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3870D5FE-AC14-4F82-BF7F-8FFD44AC7F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7AE2B77-BD33-4B42-99D4-560B6550AEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45497,7 +45497,7 @@
         <v>2</v>
       </c>
       <c r="E863" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F863" s="60">
         <v>1</v>
@@ -45547,7 +45547,7 @@
         <v>2</v>
       </c>
       <c r="E864" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F864" s="60">
         <v>1</v>
@@ -45597,7 +45597,7 @@
         <v>2</v>
       </c>
       <c r="E865" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F865" s="60">
         <v>1</v>
@@ -45647,7 +45647,7 @@
         <v>2</v>
       </c>
       <c r="E866" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F866" s="60">
         <v>1</v>
@@ -45697,7 +45697,7 @@
         <v>2</v>
       </c>
       <c r="E867" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F867" s="60">
         <v>1</v>
@@ -45747,7 +45747,7 @@
         <v>2</v>
       </c>
       <c r="E868" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F868" s="60">
         <v>1</v>
@@ -45797,7 +45797,7 @@
         <v>2</v>
       </c>
       <c r="E869" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F869" s="60">
         <v>1</v>
@@ -45847,7 +45847,7 @@
         <v>2</v>
       </c>
       <c r="E870" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F870" s="60">
         <v>1</v>
@@ -45897,7 +45897,7 @@
         <v>2</v>
       </c>
       <c r="E871" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F871" s="60">
         <v>1</v>
@@ -45947,7 +45947,7 @@
         <v>2</v>
       </c>
       <c r="E872" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F872" s="60">
         <v>1</v>
@@ -45997,7 +45997,7 @@
         <v>2</v>
       </c>
       <c r="E873" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F873" s="60">
         <v>1</v>
@@ -46047,7 +46047,7 @@
         <v>2</v>
       </c>
       <c r="E874" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F874" s="60">
         <v>1</v>
@@ -46097,7 +46097,7 @@
         <v>2</v>
       </c>
       <c r="E875" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F875" s="60">
         <v>1</v>
@@ -46147,7 +46147,7 @@
         <v>2</v>
       </c>
       <c r="E876" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F876" s="60">
         <v>1</v>
@@ -46197,7 +46197,7 @@
         <v>2</v>
       </c>
       <c r="E877" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F877" s="60">
         <v>1</v>
@@ -46247,7 +46247,7 @@
         <v>2</v>
       </c>
       <c r="E878" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F878" s="60">
         <v>1</v>
@@ -46297,7 +46297,7 @@
         <v>2</v>
       </c>
       <c r="E879" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F879" s="60">
         <v>1</v>
@@ -46347,7 +46347,7 @@
         <v>2</v>
       </c>
       <c r="E880" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F880" s="60">
         <v>1</v>
@@ -46397,7 +46397,7 @@
         <v>2</v>
       </c>
       <c r="E881" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F881" s="60">
         <v>1</v>
@@ -46447,7 +46447,7 @@
         <v>2</v>
       </c>
       <c r="E882" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F882" s="60">
         <v>1</v>
@@ -46497,7 +46497,7 @@
         <v>2</v>
       </c>
       <c r="E883" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F883" s="60">
         <v>1</v>
@@ -46547,7 +46547,7 @@
         <v>2</v>
       </c>
       <c r="E884" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F884" s="60">
         <v>1</v>
@@ -46597,7 +46597,7 @@
         <v>2</v>
       </c>
       <c r="E885" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F885" s="60">
         <v>1</v>
@@ -46647,7 +46647,7 @@
         <v>2</v>
       </c>
       <c r="E886" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F886" s="60">
         <v>1</v>
@@ -46697,7 +46697,7 @@
         <v>2</v>
       </c>
       <c r="E887" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F887" s="60">
         <v>1</v>
@@ -46747,7 +46747,7 @@
         <v>2</v>
       </c>
       <c r="E888" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F888" s="60">
         <v>1</v>
@@ -46797,7 +46797,7 @@
         <v>2</v>
       </c>
       <c r="E889" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F889" s="60">
         <v>1</v>
@@ -46847,7 +46847,7 @@
         <v>2</v>
       </c>
       <c r="E890" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F890" s="60">
         <v>1</v>
@@ -46897,7 +46897,7 @@
         <v>2</v>
       </c>
       <c r="E891" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F891" s="60">
         <v>1</v>
@@ -46947,7 +46947,7 @@
         <v>2</v>
       </c>
       <c r="E892" s="60">
-        <v>70002</v>
+        <v>70001</v>
       </c>
       <c r="F892" s="60">
         <v>1</v>
@@ -46996,8 +46996,8 @@
       <c r="D893" s="62">
         <v>2</v>
       </c>
-      <c r="E893" s="62">
-        <v>70002</v>
+      <c r="E893" s="60">
+        <v>70001</v>
       </c>
       <c r="F893" s="62">
         <v>1</v>
@@ -47046,8 +47046,8 @@
       <c r="D894" s="62">
         <v>2</v>
       </c>
-      <c r="E894" s="62">
-        <v>70002</v>
+      <c r="E894" s="60">
+        <v>70001</v>
       </c>
       <c r="F894" s="62">
         <v>1</v>
@@ -47096,8 +47096,8 @@
       <c r="D895" s="62">
         <v>2</v>
       </c>
-      <c r="E895" s="62">
-        <v>70002</v>
+      <c r="E895" s="60">
+        <v>70001</v>
       </c>
       <c r="F895" s="62">
         <v>1</v>
@@ -47146,8 +47146,8 @@
       <c r="D896" s="62">
         <v>2</v>
       </c>
-      <c r="E896" s="62">
-        <v>70002</v>
+      <c r="E896" s="60">
+        <v>70001</v>
       </c>
       <c r="F896" s="62">
         <v>1</v>
@@ -47196,8 +47196,8 @@
       <c r="D897" s="62">
         <v>2</v>
       </c>
-      <c r="E897" s="62">
-        <v>70002</v>
+      <c r="E897" s="60">
+        <v>70001</v>
       </c>
       <c r="F897" s="62">
         <v>1</v>
@@ -47246,8 +47246,8 @@
       <c r="D898" s="62">
         <v>2</v>
       </c>
-      <c r="E898" s="62">
-        <v>70002</v>
+      <c r="E898" s="60">
+        <v>70001</v>
       </c>
       <c r="F898" s="62">
         <v>1</v>
@@ -47296,8 +47296,8 @@
       <c r="D899" s="62">
         <v>2</v>
       </c>
-      <c r="E899" s="62">
-        <v>70002</v>
+      <c r="E899" s="60">
+        <v>70001</v>
       </c>
       <c r="F899" s="62">
         <v>1</v>
@@ -47346,8 +47346,8 @@
       <c r="D900" s="62">
         <v>2</v>
       </c>
-      <c r="E900" s="62">
-        <v>70002</v>
+      <c r="E900" s="60">
+        <v>70001</v>
       </c>
       <c r="F900" s="62">
         <v>1</v>
@@ -47396,8 +47396,8 @@
       <c r="D901" s="62">
         <v>2</v>
       </c>
-      <c r="E901" s="62">
-        <v>70002</v>
+      <c r="E901" s="60">
+        <v>70001</v>
       </c>
       <c r="F901" s="62">
         <v>1</v>
@@ -47446,8 +47446,8 @@
       <c r="D902" s="62">
         <v>2</v>
       </c>
-      <c r="E902" s="62">
-        <v>70002</v>
+      <c r="E902" s="60">
+        <v>70001</v>
       </c>
       <c r="F902" s="62">
         <v>1</v>
@@ -47496,8 +47496,8 @@
       <c r="D903" s="62">
         <v>2</v>
       </c>
-      <c r="E903" s="62">
-        <v>70002</v>
+      <c r="E903" s="60">
+        <v>70001</v>
       </c>
       <c r="F903" s="62">
         <v>1</v>
@@ -47546,8 +47546,8 @@
       <c r="D904" s="62">
         <v>2</v>
       </c>
-      <c r="E904" s="62">
-        <v>70002</v>
+      <c r="E904" s="60">
+        <v>70001</v>
       </c>
       <c r="F904" s="62">
         <v>1</v>
@@ -47596,8 +47596,8 @@
       <c r="D905" s="62">
         <v>2</v>
       </c>
-      <c r="E905" s="62">
-        <v>70002</v>
+      <c r="E905" s="60">
+        <v>70001</v>
       </c>
       <c r="F905" s="62">
         <v>1</v>
@@ -47646,8 +47646,8 @@
       <c r="D906" s="62">
         <v>2</v>
       </c>
-      <c r="E906" s="62">
-        <v>70002</v>
+      <c r="E906" s="60">
+        <v>70001</v>
       </c>
       <c r="F906" s="62">
         <v>1</v>
@@ -47696,8 +47696,8 @@
       <c r="D907" s="62">
         <v>2</v>
       </c>
-      <c r="E907" s="62">
-        <v>70002</v>
+      <c r="E907" s="60">
+        <v>70001</v>
       </c>
       <c r="F907" s="62">
         <v>1</v>
@@ -47746,8 +47746,8 @@
       <c r="D908" s="62">
         <v>2</v>
       </c>
-      <c r="E908" s="62">
-        <v>70002</v>
+      <c r="E908" s="60">
+        <v>70001</v>
       </c>
       <c r="F908" s="62">
         <v>1</v>
@@ -47796,8 +47796,8 @@
       <c r="D909" s="62">
         <v>2</v>
       </c>
-      <c r="E909" s="62">
-        <v>70002</v>
+      <c r="E909" s="60">
+        <v>70001</v>
       </c>
       <c r="F909" s="62">
         <v>1</v>
@@ -47846,8 +47846,8 @@
       <c r="D910" s="62">
         <v>2</v>
       </c>
-      <c r="E910" s="62">
-        <v>70002</v>
+      <c r="E910" s="60">
+        <v>70001</v>
       </c>
       <c r="F910" s="62">
         <v>1</v>
@@ -47896,8 +47896,8 @@
       <c r="D911" s="62">
         <v>2</v>
       </c>
-      <c r="E911" s="62">
-        <v>70002</v>
+      <c r="E911" s="60">
+        <v>70001</v>
       </c>
       <c r="F911" s="62">
         <v>1</v>
@@ -47946,8 +47946,8 @@
       <c r="D912" s="62">
         <v>2</v>
       </c>
-      <c r="E912" s="62">
-        <v>70002</v>
+      <c r="E912" s="60">
+        <v>70001</v>
       </c>
       <c r="F912" s="62">
         <v>1</v>
@@ -47996,8 +47996,8 @@
       <c r="D913" s="62">
         <v>2</v>
       </c>
-      <c r="E913" s="62">
-        <v>70002</v>
+      <c r="E913" s="60">
+        <v>70001</v>
       </c>
       <c r="F913" s="62">
         <v>1</v>
@@ -48046,8 +48046,8 @@
       <c r="D914" s="62">
         <v>2</v>
       </c>
-      <c r="E914" s="62">
-        <v>70002</v>
+      <c r="E914" s="60">
+        <v>70001</v>
       </c>
       <c r="F914" s="62">
         <v>1</v>
@@ -48096,8 +48096,8 @@
       <c r="D915" s="62">
         <v>2</v>
       </c>
-      <c r="E915" s="62">
-        <v>70002</v>
+      <c r="E915" s="60">
+        <v>70001</v>
       </c>
       <c r="F915" s="62">
         <v>1</v>
@@ -48146,8 +48146,8 @@
       <c r="D916" s="62">
         <v>2</v>
       </c>
-      <c r="E916" s="62">
-        <v>70002</v>
+      <c r="E916" s="60">
+        <v>70001</v>
       </c>
       <c r="F916" s="62">
         <v>1</v>
@@ -48196,8 +48196,8 @@
       <c r="D917" s="62">
         <v>2</v>
       </c>
-      <c r="E917" s="62">
-        <v>70002</v>
+      <c r="E917" s="60">
+        <v>70001</v>
       </c>
       <c r="F917" s="62">
         <v>1</v>
@@ -48246,8 +48246,8 @@
       <c r="D918" s="62">
         <v>2</v>
       </c>
-      <c r="E918" s="62">
-        <v>70002</v>
+      <c r="E918" s="60">
+        <v>70001</v>
       </c>
       <c r="F918" s="62">
         <v>1</v>
@@ -48296,8 +48296,8 @@
       <c r="D919" s="62">
         <v>2</v>
       </c>
-      <c r="E919" s="62">
-        <v>70002</v>
+      <c r="E919" s="60">
+        <v>70001</v>
       </c>
       <c r="F919" s="62">
         <v>1</v>
@@ -48346,8 +48346,8 @@
       <c r="D920" s="62">
         <v>2</v>
       </c>
-      <c r="E920" s="62">
-        <v>70002</v>
+      <c r="E920" s="60">
+        <v>70001</v>
       </c>
       <c r="F920" s="62">
         <v>1</v>
@@ -48396,8 +48396,8 @@
       <c r="D921" s="62">
         <v>2</v>
       </c>
-      <c r="E921" s="62">
-        <v>70002</v>
+      <c r="E921" s="60">
+        <v>70001</v>
       </c>
       <c r="F921" s="62">
         <v>1</v>
@@ -48446,8 +48446,8 @@
       <c r="D922" s="62">
         <v>2</v>
       </c>
-      <c r="E922" s="62">
-        <v>70002</v>
+      <c r="E922" s="60">
+        <v>70001</v>
       </c>
       <c r="F922" s="62">
         <v>1</v>
@@ -48496,8 +48496,8 @@
       <c r="D923" s="62">
         <v>2</v>
       </c>
-      <c r="E923" s="62">
-        <v>70002</v>
+      <c r="E923" s="60">
+        <v>70001</v>
       </c>
       <c r="F923" s="62">
         <v>1</v>
@@ -48546,8 +48546,8 @@
       <c r="D924" s="62">
         <v>2</v>
       </c>
-      <c r="E924" s="62">
-        <v>70002</v>
+      <c r="E924" s="60">
+        <v>70001</v>
       </c>
       <c r="F924" s="62">
         <v>1</v>
@@ -48596,8 +48596,8 @@
       <c r="D925" s="62">
         <v>2</v>
       </c>
-      <c r="E925" s="62">
-        <v>70002</v>
+      <c r="E925" s="60">
+        <v>70001</v>
       </c>
       <c r="F925" s="62">
         <v>1</v>
@@ -48646,8 +48646,8 @@
       <c r="D926" s="62">
         <v>2</v>
       </c>
-      <c r="E926" s="62">
-        <v>70002</v>
+      <c r="E926" s="60">
+        <v>70001</v>
       </c>
       <c r="F926" s="62">
         <v>1</v>
@@ -48696,8 +48696,8 @@
       <c r="D927" s="62">
         <v>2</v>
       </c>
-      <c r="E927" s="62">
-        <v>70002</v>
+      <c r="E927" s="60">
+        <v>70001</v>
       </c>
       <c r="F927" s="62">
         <v>1</v>
@@ -48746,8 +48746,8 @@
       <c r="D928" s="62">
         <v>2</v>
       </c>
-      <c r="E928" s="62">
-        <v>70002</v>
+      <c r="E928" s="60">
+        <v>70001</v>
       </c>
       <c r="F928" s="62">
         <v>1</v>
@@ -48796,8 +48796,8 @@
       <c r="D929" s="62">
         <v>2</v>
       </c>
-      <c r="E929" s="62">
-        <v>70002</v>
+      <c r="E929" s="60">
+        <v>70001</v>
       </c>
       <c r="F929" s="62">
         <v>1</v>
@@ -48846,8 +48846,8 @@
       <c r="D930" s="62">
         <v>2</v>
       </c>
-      <c r="E930" s="62">
-        <v>70002</v>
+      <c r="E930" s="60">
+        <v>70001</v>
       </c>
       <c r="F930" s="62">
         <v>1</v>
@@ -48896,8 +48896,8 @@
       <c r="D931" s="62">
         <v>2</v>
       </c>
-      <c r="E931" s="62">
-        <v>70002</v>
+      <c r="E931" s="60">
+        <v>70001</v>
       </c>
       <c r="F931" s="62">
         <v>1</v>
@@ -48946,8 +48946,8 @@
       <c r="D932" s="62">
         <v>2</v>
       </c>
-      <c r="E932" s="62">
-        <v>70002</v>
+      <c r="E932" s="60">
+        <v>70001</v>
       </c>
       <c r="F932" s="62">
         <v>1</v>
@@ -48996,8 +48996,8 @@
       <c r="D933" s="62">
         <v>2</v>
       </c>
-      <c r="E933" s="62">
-        <v>70002</v>
+      <c r="E933" s="60">
+        <v>70001</v>
       </c>
       <c r="F933" s="62">
         <v>1</v>
@@ -49046,8 +49046,8 @@
       <c r="D934" s="62">
         <v>2</v>
       </c>
-      <c r="E934" s="62">
-        <v>70002</v>
+      <c r="E934" s="60">
+        <v>70001</v>
       </c>
       <c r="F934" s="62">
         <v>1</v>
@@ -49096,8 +49096,8 @@
       <c r="D935" s="62">
         <v>2</v>
       </c>
-      <c r="E935" s="62">
-        <v>70002</v>
+      <c r="E935" s="60">
+        <v>70001</v>
       </c>
       <c r="F935" s="62">
         <v>1</v>
@@ -49146,8 +49146,8 @@
       <c r="D936" s="62">
         <v>2</v>
       </c>
-      <c r="E936" s="62">
-        <v>70002</v>
+      <c r="E936" s="60">
+        <v>70001</v>
       </c>
       <c r="F936" s="62">
         <v>1</v>
@@ -49196,8 +49196,8 @@
       <c r="D937" s="62">
         <v>2</v>
       </c>
-      <c r="E937" s="62">
-        <v>70002</v>
+      <c r="E937" s="60">
+        <v>70001</v>
       </c>
       <c r="F937" s="62">
         <v>1</v>
@@ -49246,8 +49246,8 @@
       <c r="D938" s="62">
         <v>2</v>
       </c>
-      <c r="E938" s="62">
-        <v>70002</v>
+      <c r="E938" s="60">
+        <v>70001</v>
       </c>
       <c r="F938" s="62">
         <v>1</v>
@@ -49296,8 +49296,8 @@
       <c r="D939" s="62">
         <v>2</v>
       </c>
-      <c r="E939" s="62">
-        <v>70002</v>
+      <c r="E939" s="60">
+        <v>70001</v>
       </c>
       <c r="F939" s="62">
         <v>1</v>
@@ -49346,8 +49346,8 @@
       <c r="D940" s="65">
         <v>2</v>
       </c>
-      <c r="E940" s="65">
-        <v>70002</v>
+      <c r="E940" s="60">
+        <v>70001</v>
       </c>
       <c r="F940" s="65">
         <v>1</v>
@@ -49396,8 +49396,8 @@
       <c r="D941" s="62">
         <v>3</v>
       </c>
-      <c r="E941" s="62">
-        <v>70003</v>
+      <c r="E941" s="60">
+        <v>70001</v>
       </c>
       <c r="F941" s="62">
         <v>1</v>
@@ -49446,8 +49446,8 @@
       <c r="D942" s="62">
         <v>3</v>
       </c>
-      <c r="E942" s="62">
-        <v>70003</v>
+      <c r="E942" s="60">
+        <v>70001</v>
       </c>
       <c r="F942" s="62">
         <v>1</v>
@@ -49496,8 +49496,8 @@
       <c r="D943" s="62">
         <v>3</v>
       </c>
-      <c r="E943" s="62">
-        <v>70003</v>
+      <c r="E943" s="60">
+        <v>70001</v>
       </c>
       <c r="F943" s="62">
         <v>1</v>
@@ -49546,8 +49546,8 @@
       <c r="D944" s="62">
         <v>3</v>
       </c>
-      <c r="E944" s="62">
-        <v>70003</v>
+      <c r="E944" s="60">
+        <v>70001</v>
       </c>
       <c r="F944" s="62">
         <v>1</v>
@@ -49596,8 +49596,8 @@
       <c r="D945" s="62">
         <v>3</v>
       </c>
-      <c r="E945" s="62">
-        <v>70003</v>
+      <c r="E945" s="60">
+        <v>70001</v>
       </c>
       <c r="F945" s="62">
         <v>1</v>
@@ -49646,8 +49646,8 @@
       <c r="D946" s="62">
         <v>3</v>
       </c>
-      <c r="E946" s="62">
-        <v>70003</v>
+      <c r="E946" s="60">
+        <v>70001</v>
       </c>
       <c r="F946" s="62">
         <v>1</v>
@@ -49696,8 +49696,8 @@
       <c r="D947" s="62">
         <v>3</v>
       </c>
-      <c r="E947" s="62">
-        <v>70003</v>
+      <c r="E947" s="60">
+        <v>70001</v>
       </c>
       <c r="F947" s="62">
         <v>1</v>
@@ -49746,8 +49746,8 @@
       <c r="D948" s="62">
         <v>3</v>
       </c>
-      <c r="E948" s="62">
-        <v>70003</v>
+      <c r="E948" s="60">
+        <v>70001</v>
       </c>
       <c r="F948" s="62">
         <v>1</v>
@@ -49796,8 +49796,8 @@
       <c r="D949" s="62">
         <v>3</v>
       </c>
-      <c r="E949" s="62">
-        <v>70003</v>
+      <c r="E949" s="60">
+        <v>70001</v>
       </c>
       <c r="F949" s="62">
         <v>1</v>
@@ -49846,8 +49846,8 @@
       <c r="D950" s="62">
         <v>3</v>
       </c>
-      <c r="E950" s="62">
-        <v>70003</v>
+      <c r="E950" s="60">
+        <v>70001</v>
       </c>
       <c r="F950" s="62">
         <v>1</v>
@@ -49896,8 +49896,8 @@
       <c r="D951" s="62">
         <v>3</v>
       </c>
-      <c r="E951" s="62">
-        <v>70003</v>
+      <c r="E951" s="60">
+        <v>70001</v>
       </c>
       <c r="F951" s="62">
         <v>1</v>
@@ -49946,8 +49946,8 @@
       <c r="D952" s="62">
         <v>3</v>
       </c>
-      <c r="E952" s="62">
-        <v>70003</v>
+      <c r="E952" s="60">
+        <v>70001</v>
       </c>
       <c r="F952" s="62">
         <v>1</v>
@@ -49996,8 +49996,8 @@
       <c r="D953" s="62">
         <v>3</v>
       </c>
-      <c r="E953" s="62">
-        <v>70003</v>
+      <c r="E953" s="60">
+        <v>70001</v>
       </c>
       <c r="F953" s="62">
         <v>1</v>
@@ -50046,8 +50046,8 @@
       <c r="D954" s="62">
         <v>3</v>
       </c>
-      <c r="E954" s="62">
-        <v>70003</v>
+      <c r="E954" s="60">
+        <v>70001</v>
       </c>
       <c r="F954" s="62">
         <v>1</v>
@@ -50096,8 +50096,8 @@
       <c r="D955" s="62">
         <v>3</v>
       </c>
-      <c r="E955" s="62">
-        <v>70003</v>
+      <c r="E955" s="60">
+        <v>70001</v>
       </c>
       <c r="F955" s="62">
         <v>1</v>
@@ -50146,8 +50146,8 @@
       <c r="D956" s="62">
         <v>3</v>
       </c>
-      <c r="E956" s="62">
-        <v>70003</v>
+      <c r="E956" s="60">
+        <v>70001</v>
       </c>
       <c r="F956" s="62">
         <v>1</v>
@@ -50196,8 +50196,8 @@
       <c r="D957" s="62">
         <v>3</v>
       </c>
-      <c r="E957" s="62">
-        <v>70003</v>
+      <c r="E957" s="60">
+        <v>70001</v>
       </c>
       <c r="F957" s="62">
         <v>1</v>
@@ -50246,8 +50246,8 @@
       <c r="D958" s="62">
         <v>3</v>
       </c>
-      <c r="E958" s="62">
-        <v>70003</v>
+      <c r="E958" s="60">
+        <v>70001</v>
       </c>
       <c r="F958" s="62">
         <v>1</v>
@@ -50296,8 +50296,8 @@
       <c r="D959" s="67">
         <v>3</v>
       </c>
-      <c r="E959" s="67">
-        <v>70003</v>
+      <c r="E959" s="60">
+        <v>70001</v>
       </c>
       <c r="F959" s="67">
         <v>1</v>
@@ -50346,8 +50346,8 @@
       <c r="D960" s="62">
         <v>3</v>
       </c>
-      <c r="E960" s="62">
-        <v>70003</v>
+      <c r="E960" s="60">
+        <v>70001</v>
       </c>
       <c r="F960" s="62">
         <v>1</v>
@@ -50396,8 +50396,8 @@
       <c r="D961" s="62">
         <v>3</v>
       </c>
-      <c r="E961" s="62">
-        <v>70003</v>
+      <c r="E961" s="60">
+        <v>70001</v>
       </c>
       <c r="F961" s="62">
         <v>1</v>
@@ -50446,8 +50446,8 @@
       <c r="D962" s="62">
         <v>3</v>
       </c>
-      <c r="E962" s="62">
-        <v>70003</v>
+      <c r="E962" s="60">
+        <v>70001</v>
       </c>
       <c r="F962" s="62">
         <v>1</v>
@@ -50496,8 +50496,8 @@
       <c r="D963" s="62">
         <v>3</v>
       </c>
-      <c r="E963" s="62">
-        <v>70003</v>
+      <c r="E963" s="60">
+        <v>70001</v>
       </c>
       <c r="F963" s="62">
         <v>1</v>
@@ -50546,8 +50546,8 @@
       <c r="D964" s="62">
         <v>3</v>
       </c>
-      <c r="E964" s="62">
-        <v>70003</v>
+      <c r="E964" s="60">
+        <v>70001</v>
       </c>
       <c r="F964" s="62">
         <v>1</v>
@@ -50596,8 +50596,8 @@
       <c r="D965" s="62">
         <v>3</v>
       </c>
-      <c r="E965" s="62">
-        <v>70003</v>
+      <c r="E965" s="60">
+        <v>70001</v>
       </c>
       <c r="F965" s="62">
         <v>1</v>
@@ -50646,8 +50646,8 @@
       <c r="D966" s="69">
         <v>3</v>
       </c>
-      <c r="E966" s="69">
-        <v>70003</v>
+      <c r="E966" s="60">
+        <v>70001</v>
       </c>
       <c r="F966" s="69">
         <v>1</v>
@@ -50696,8 +50696,8 @@
       <c r="D967" s="62">
         <v>3</v>
       </c>
-      <c r="E967" s="62">
-        <v>70003</v>
+      <c r="E967" s="60">
+        <v>70001</v>
       </c>
       <c r="F967" s="62">
         <v>1</v>
@@ -50746,8 +50746,8 @@
       <c r="D968" s="62">
         <v>3</v>
       </c>
-      <c r="E968" s="62">
-        <v>70003</v>
+      <c r="E968" s="60">
+        <v>70001</v>
       </c>
       <c r="F968" s="62">
         <v>1</v>
@@ -50796,8 +50796,8 @@
       <c r="D969" s="62">
         <v>3</v>
       </c>
-      <c r="E969" s="62">
-        <v>70003</v>
+      <c r="E969" s="60">
+        <v>70001</v>
       </c>
       <c r="F969" s="62">
         <v>1</v>
@@ -50846,8 +50846,8 @@
       <c r="D970" s="62">
         <v>3</v>
       </c>
-      <c r="E970" s="62">
-        <v>70003</v>
+      <c r="E970" s="60">
+        <v>70001</v>
       </c>
       <c r="F970" s="62">
         <v>1</v>
@@ -50896,8 +50896,8 @@
       <c r="D971" s="62">
         <v>3</v>
       </c>
-      <c r="E971" s="62">
-        <v>70003</v>
+      <c r="E971" s="60">
+        <v>70001</v>
       </c>
       <c r="F971" s="62">
         <v>1</v>
@@ -50946,8 +50946,8 @@
       <c r="D972" s="62">
         <v>3</v>
       </c>
-      <c r="E972" s="62">
-        <v>70003</v>
+      <c r="E972" s="60">
+        <v>70001</v>
       </c>
       <c r="F972" s="62">
         <v>1</v>
@@ -50996,8 +50996,8 @@
       <c r="D973" s="62">
         <v>3</v>
       </c>
-      <c r="E973" s="62">
-        <v>70003</v>
+      <c r="E973" s="60">
+        <v>70001</v>
       </c>
       <c r="F973" s="62">
         <v>1</v>
@@ -51046,8 +51046,8 @@
       <c r="D974" s="62">
         <v>3</v>
       </c>
-      <c r="E974" s="62">
-        <v>70003</v>
+      <c r="E974" s="60">
+        <v>70001</v>
       </c>
       <c r="F974" s="62">
         <v>1</v>
@@ -51096,8 +51096,8 @@
       <c r="D975" s="69">
         <v>3</v>
       </c>
-      <c r="E975" s="69">
-        <v>70003</v>
+      <c r="E975" s="60">
+        <v>70001</v>
       </c>
       <c r="F975" s="69">
         <v>1</v>
@@ -51146,8 +51146,8 @@
       <c r="D976" s="62">
         <v>3</v>
       </c>
-      <c r="E976" s="62">
-        <v>70003</v>
+      <c r="E976" s="60">
+        <v>70001</v>
       </c>
       <c r="F976" s="62">
         <v>1</v>
@@ -51196,8 +51196,8 @@
       <c r="D977" s="62">
         <v>3</v>
       </c>
-      <c r="E977" s="62">
-        <v>70003</v>
+      <c r="E977" s="60">
+        <v>70001</v>
       </c>
       <c r="F977" s="62">
         <v>1</v>
@@ -51246,8 +51246,8 @@
       <c r="D978" s="62">
         <v>3</v>
       </c>
-      <c r="E978" s="62">
-        <v>70003</v>
+      <c r="E978" s="60">
+        <v>70001</v>
       </c>
       <c r="F978" s="62">
         <v>1</v>
@@ -51296,8 +51296,8 @@
       <c r="D979" s="62">
         <v>3</v>
       </c>
-      <c r="E979" s="62">
-        <v>70003</v>
+      <c r="E979" s="60">
+        <v>70001</v>
       </c>
       <c r="F979" s="62">
         <v>1</v>
@@ -51346,8 +51346,8 @@
       <c r="D980" s="62">
         <v>3</v>
       </c>
-      <c r="E980" s="62">
-        <v>70003</v>
+      <c r="E980" s="60">
+        <v>70001</v>
       </c>
       <c r="F980" s="62">
         <v>1</v>
@@ -51396,8 +51396,8 @@
       <c r="D981" s="62">
         <v>3</v>
       </c>
-      <c r="E981" s="62">
-        <v>70003</v>
+      <c r="E981" s="60">
+        <v>70001</v>
       </c>
       <c r="F981" s="62">
         <v>1</v>
@@ -51446,8 +51446,8 @@
       <c r="D982" s="62">
         <v>3</v>
       </c>
-      <c r="E982" s="62">
-        <v>70003</v>
+      <c r="E982" s="60">
+        <v>70001</v>
       </c>
       <c r="F982" s="62">
         <v>1</v>
@@ -51496,8 +51496,8 @@
       <c r="D983" s="62">
         <v>3</v>
       </c>
-      <c r="E983" s="62">
-        <v>70003</v>
+      <c r="E983" s="60">
+        <v>70001</v>
       </c>
       <c r="F983" s="62">
         <v>1</v>
@@ -51546,8 +51546,8 @@
       <c r="D984" s="62">
         <v>3</v>
       </c>
-      <c r="E984" s="62">
-        <v>70003</v>
+      <c r="E984" s="60">
+        <v>70001</v>
       </c>
       <c r="F984" s="62">
         <v>1</v>
@@ -51596,8 +51596,8 @@
       <c r="D985" s="69">
         <v>3</v>
       </c>
-      <c r="E985" s="69">
-        <v>70003</v>
+      <c r="E985" s="60">
+        <v>70001</v>
       </c>
       <c r="F985" s="69">
         <v>1</v>
@@ -51646,8 +51646,8 @@
       <c r="D986" s="62">
         <v>3</v>
       </c>
-      <c r="E986" s="62">
-        <v>70003</v>
+      <c r="E986" s="60">
+        <v>70001</v>
       </c>
       <c r="F986" s="62">
         <v>1</v>
@@ -51696,8 +51696,8 @@
       <c r="D987" s="62">
         <v>3</v>
       </c>
-      <c r="E987" s="62">
-        <v>70003</v>
+      <c r="E987" s="60">
+        <v>70001</v>
       </c>
       <c r="F987" s="62">
         <v>1</v>
@@ -51746,8 +51746,8 @@
       <c r="D988" s="62">
         <v>3</v>
       </c>
-      <c r="E988" s="62">
-        <v>70003</v>
+      <c r="E988" s="60">
+        <v>70001</v>
       </c>
       <c r="F988" s="62">
         <v>1</v>
@@ -51796,8 +51796,8 @@
       <c r="D989" s="62">
         <v>3</v>
       </c>
-      <c r="E989" s="62">
-        <v>70003</v>
+      <c r="E989" s="60">
+        <v>70001</v>
       </c>
       <c r="F989" s="62">
         <v>1</v>
@@ -51846,8 +51846,8 @@
       <c r="D990" s="62">
         <v>3</v>
       </c>
-      <c r="E990" s="62">
-        <v>70003</v>
+      <c r="E990" s="60">
+        <v>70001</v>
       </c>
       <c r="F990" s="62">
         <v>1</v>
@@ -51896,8 +51896,8 @@
       <c r="D991" s="62">
         <v>3</v>
       </c>
-      <c r="E991" s="62">
-        <v>70003</v>
+      <c r="E991" s="60">
+        <v>70001</v>
       </c>
       <c r="F991" s="62">
         <v>1</v>
@@ -51946,8 +51946,8 @@
       <c r="D992" s="62">
         <v>3</v>
       </c>
-      <c r="E992" s="62">
-        <v>70003</v>
+      <c r="E992" s="60">
+        <v>70001</v>
       </c>
       <c r="F992" s="62">
         <v>1</v>
@@ -51996,8 +51996,8 @@
       <c r="D993" s="62">
         <v>3</v>
       </c>
-      <c r="E993" s="62">
-        <v>70003</v>
+      <c r="E993" s="60">
+        <v>70001</v>
       </c>
       <c r="F993" s="62">
         <v>1</v>
@@ -52046,8 +52046,8 @@
       <c r="D994" s="62">
         <v>3</v>
       </c>
-      <c r="E994" s="62">
-        <v>70003</v>
+      <c r="E994" s="60">
+        <v>70001</v>
       </c>
       <c r="F994" s="62">
         <v>1</v>
@@ -52096,8 +52096,8 @@
       <c r="D995" s="62">
         <v>3</v>
       </c>
-      <c r="E995" s="62">
-        <v>70003</v>
+      <c r="E995" s="60">
+        <v>70001</v>
       </c>
       <c r="F995" s="62">
         <v>1</v>
@@ -52146,8 +52146,8 @@
       <c r="D996" s="69">
         <v>3</v>
       </c>
-      <c r="E996" s="69">
-        <v>70003</v>
+      <c r="E996" s="60">
+        <v>70001</v>
       </c>
       <c r="F996" s="69">
         <v>1</v>
@@ -52196,8 +52196,8 @@
       <c r="D997" s="62">
         <v>3</v>
       </c>
-      <c r="E997" s="62">
-        <v>70003</v>
+      <c r="E997" s="60">
+        <v>70001</v>
       </c>
       <c r="F997" s="62">
         <v>1</v>
@@ -52246,8 +52246,8 @@
       <c r="D998" s="62">
         <v>3</v>
       </c>
-      <c r="E998" s="62">
-        <v>70003</v>
+      <c r="E998" s="60">
+        <v>70001</v>
       </c>
       <c r="F998" s="62">
         <v>1</v>
@@ -52296,8 +52296,8 @@
       <c r="D999" s="62">
         <v>3</v>
       </c>
-      <c r="E999" s="62">
-        <v>70003</v>
+      <c r="E999" s="60">
+        <v>70001</v>
       </c>
       <c r="F999" s="62">
         <v>1</v>
@@ -52346,8 +52346,8 @@
       <c r="D1000" s="62">
         <v>3</v>
       </c>
-      <c r="E1000" s="62">
-        <v>70003</v>
+      <c r="E1000" s="60">
+        <v>70001</v>
       </c>
       <c r="F1000" s="62">
         <v>1</v>
@@ -52396,8 +52396,8 @@
       <c r="D1001" s="62">
         <v>3</v>
       </c>
-      <c r="E1001" s="62">
-        <v>70003</v>
+      <c r="E1001" s="60">
+        <v>70001</v>
       </c>
       <c r="F1001" s="62">
         <v>1</v>
@@ -52446,8 +52446,8 @@
       <c r="D1002" s="62">
         <v>3</v>
       </c>
-      <c r="E1002" s="62">
-        <v>70003</v>
+      <c r="E1002" s="60">
+        <v>70001</v>
       </c>
       <c r="F1002" s="62">
         <v>1</v>
@@ -52496,8 +52496,8 @@
       <c r="D1003" s="62">
         <v>3</v>
       </c>
-      <c r="E1003" s="62">
-        <v>70003</v>
+      <c r="E1003" s="60">
+        <v>70001</v>
       </c>
       <c r="F1003" s="62">
         <v>1</v>
@@ -52546,8 +52546,8 @@
       <c r="D1004" s="62">
         <v>3</v>
       </c>
-      <c r="E1004" s="62">
-        <v>70003</v>
+      <c r="E1004" s="60">
+        <v>70001</v>
       </c>
       <c r="F1004" s="62">
         <v>1</v>
@@ -52596,8 +52596,8 @@
       <c r="D1005" s="62">
         <v>3</v>
       </c>
-      <c r="E1005" s="62">
-        <v>70003</v>
+      <c r="E1005" s="60">
+        <v>70001</v>
       </c>
       <c r="F1005" s="62">
         <v>1</v>
@@ -52646,8 +52646,8 @@
       <c r="D1006" s="62">
         <v>3</v>
       </c>
-      <c r="E1006" s="62">
-        <v>70003</v>
+      <c r="E1006" s="60">
+        <v>70001</v>
       </c>
       <c r="F1006" s="62">
         <v>1</v>
@@ -52696,8 +52696,8 @@
       <c r="D1007" s="62">
         <v>3</v>
       </c>
-      <c r="E1007" s="62">
-        <v>70003</v>
+      <c r="E1007" s="60">
+        <v>70001</v>
       </c>
       <c r="F1007" s="62">
         <v>1</v>
@@ -52746,8 +52746,8 @@
       <c r="D1008" s="69">
         <v>3</v>
       </c>
-      <c r="E1008" s="69">
-        <v>70003</v>
+      <c r="E1008" s="60">
+        <v>70001</v>
       </c>
       <c r="F1008" s="69">
         <v>1</v>
@@ -52796,8 +52796,8 @@
       <c r="D1009" s="62">
         <v>3</v>
       </c>
-      <c r="E1009" s="62">
-        <v>70003</v>
+      <c r="E1009" s="60">
+        <v>70001</v>
       </c>
       <c r="F1009" s="62">
         <v>1</v>
@@ -52846,8 +52846,8 @@
       <c r="D1010" s="62">
         <v>3</v>
       </c>
-      <c r="E1010" s="62">
-        <v>70003</v>
+      <c r="E1010" s="60">
+        <v>70001</v>
       </c>
       <c r="F1010" s="62">
         <v>1</v>
@@ -52896,8 +52896,8 @@
       <c r="D1011" s="62">
         <v>3</v>
       </c>
-      <c r="E1011" s="62">
-        <v>70003</v>
+      <c r="E1011" s="60">
+        <v>70001</v>
       </c>
       <c r="F1011" s="62">
         <v>1</v>
@@ -52946,8 +52946,8 @@
       <c r="D1012" s="62">
         <v>3</v>
       </c>
-      <c r="E1012" s="62">
-        <v>70003</v>
+      <c r="E1012" s="60">
+        <v>70001</v>
       </c>
       <c r="F1012" s="62">
         <v>1</v>
@@ -52996,8 +52996,8 @@
       <c r="D1013" s="62">
         <v>3</v>
       </c>
-      <c r="E1013" s="62">
-        <v>70003</v>
+      <c r="E1013" s="60">
+        <v>70001</v>
       </c>
       <c r="F1013" s="62">
         <v>1</v>
@@ -53046,8 +53046,8 @@
       <c r="D1014" s="62">
         <v>3</v>
       </c>
-      <c r="E1014" s="62">
-        <v>70003</v>
+      <c r="E1014" s="60">
+        <v>70001</v>
       </c>
       <c r="F1014" s="62">
         <v>1</v>
@@ -53096,8 +53096,8 @@
       <c r="D1015" s="62">
         <v>3</v>
       </c>
-      <c r="E1015" s="62">
-        <v>70003</v>
+      <c r="E1015" s="60">
+        <v>70001</v>
       </c>
       <c r="F1015" s="62">
         <v>1</v>
@@ -53146,8 +53146,8 @@
       <c r="D1016" s="62">
         <v>3</v>
       </c>
-      <c r="E1016" s="62">
-        <v>70003</v>
+      <c r="E1016" s="60">
+        <v>70001</v>
       </c>
       <c r="F1016" s="62">
         <v>1</v>
@@ -53196,8 +53196,8 @@
       <c r="D1017" s="62">
         <v>3</v>
       </c>
-      <c r="E1017" s="62">
-        <v>70003</v>
+      <c r="E1017" s="60">
+        <v>70001</v>
       </c>
       <c r="F1017" s="62">
         <v>1</v>
@@ -53246,8 +53246,8 @@
       <c r="D1018" s="62">
         <v>3</v>
       </c>
-      <c r="E1018" s="62">
-        <v>70003</v>
+      <c r="E1018" s="60">
+        <v>70001</v>
       </c>
       <c r="F1018" s="62">
         <v>1</v>
@@ -53296,8 +53296,8 @@
       <c r="D1019" s="62">
         <v>3</v>
       </c>
-      <c r="E1019" s="62">
-        <v>70003</v>
+      <c r="E1019" s="60">
+        <v>70001</v>
       </c>
       <c r="F1019" s="62">
         <v>1</v>
@@ -53346,8 +53346,8 @@
       <c r="D1020" s="62">
         <v>3</v>
       </c>
-      <c r="E1020" s="62">
-        <v>70003</v>
+      <c r="E1020" s="60">
+        <v>70001</v>
       </c>
       <c r="F1020" s="62">
         <v>1</v>
@@ -53396,8 +53396,8 @@
       <c r="D1021" s="62">
         <v>3</v>
       </c>
-      <c r="E1021" s="62">
-        <v>70003</v>
+      <c r="E1021" s="60">
+        <v>70001</v>
       </c>
       <c r="F1021" s="62">
         <v>1</v>
@@ -53446,8 +53446,8 @@
       <c r="D1022" s="62">
         <v>4</v>
       </c>
-      <c r="E1022" s="62">
-        <v>70004</v>
+      <c r="E1022" s="60">
+        <v>70001</v>
       </c>
       <c r="F1022" s="62">
         <v>1</v>
@@ -53496,8 +53496,8 @@
       <c r="D1023" s="62">
         <v>4</v>
       </c>
-      <c r="E1023" s="62">
-        <v>70004</v>
+      <c r="E1023" s="60">
+        <v>70001</v>
       </c>
       <c r="F1023" s="62">
         <v>1</v>
@@ -53546,8 +53546,8 @@
       <c r="D1024" s="71">
         <v>4</v>
       </c>
-      <c r="E1024" s="71">
-        <v>70004</v>
+      <c r="E1024" s="60">
+        <v>70001</v>
       </c>
       <c r="F1024" s="71">
         <v>1</v>
@@ -53596,8 +53596,8 @@
       <c r="D1025" s="62">
         <v>4</v>
       </c>
-      <c r="E1025" s="62">
-        <v>70004</v>
+      <c r="E1025" s="60">
+        <v>70001</v>
       </c>
       <c r="F1025" s="62">
         <v>1</v>
@@ -53646,8 +53646,8 @@
       <c r="D1026" s="62">
         <v>4</v>
       </c>
-      <c r="E1026" s="62">
-        <v>70004</v>
+      <c r="E1026" s="60">
+        <v>70001</v>
       </c>
       <c r="F1026" s="62">
         <v>1</v>
@@ -53696,8 +53696,8 @@
       <c r="D1027" s="62">
         <v>4</v>
       </c>
-      <c r="E1027" s="62">
-        <v>70004</v>
+      <c r="E1027" s="60">
+        <v>70001</v>
       </c>
       <c r="F1027" s="62">
         <v>1</v>
@@ -53746,8 +53746,8 @@
       <c r="D1028" s="69">
         <v>4</v>
       </c>
-      <c r="E1028" s="69">
-        <v>70004</v>
+      <c r="E1028" s="60">
+        <v>70001</v>
       </c>
       <c r="F1028" s="69">
         <v>1</v>
@@ -53796,8 +53796,8 @@
       <c r="D1029" s="62">
         <v>4</v>
       </c>
-      <c r="E1029" s="62">
-        <v>70004</v>
+      <c r="E1029" s="60">
+        <v>70001</v>
       </c>
       <c r="F1029" s="62">
         <v>1</v>
@@ -53846,8 +53846,8 @@
       <c r="D1030" s="62">
         <v>4</v>
       </c>
-      <c r="E1030" s="62">
-        <v>70004</v>
+      <c r="E1030" s="60">
+        <v>70001</v>
       </c>
       <c r="F1030" s="62">
         <v>1</v>
@@ -53896,8 +53896,8 @@
       <c r="D1031" s="62">
         <v>4</v>
       </c>
-      <c r="E1031" s="62">
-        <v>70004</v>
+      <c r="E1031" s="60">
+        <v>70001</v>
       </c>
       <c r="F1031" s="62">
         <v>1</v>
@@ -53946,8 +53946,8 @@
       <c r="D1032" s="62">
         <v>4</v>
       </c>
-      <c r="E1032" s="62">
-        <v>70004</v>
+      <c r="E1032" s="60">
+        <v>70001</v>
       </c>
       <c r="F1032" s="62">
         <v>1</v>
@@ -53996,8 +53996,8 @@
       <c r="D1033" s="69">
         <v>4</v>
       </c>
-      <c r="E1033" s="69">
-        <v>70004</v>
+      <c r="E1033" s="60">
+        <v>70001</v>
       </c>
       <c r="F1033" s="69">
         <v>1</v>
@@ -54046,8 +54046,8 @@
       <c r="D1034" s="62">
         <v>4</v>
       </c>
-      <c r="E1034" s="62">
-        <v>70004</v>
+      <c r="E1034" s="60">
+        <v>70001</v>
       </c>
       <c r="F1034" s="62">
         <v>1</v>
@@ -54096,8 +54096,8 @@
       <c r="D1035" s="62">
         <v>4</v>
       </c>
-      <c r="E1035" s="62">
-        <v>70004</v>
+      <c r="E1035" s="60">
+        <v>70001</v>
       </c>
       <c r="F1035" s="62">
         <v>1</v>
@@ -54146,8 +54146,8 @@
       <c r="D1036" s="62">
         <v>4</v>
       </c>
-      <c r="E1036" s="62">
-        <v>70004</v>
+      <c r="E1036" s="60">
+        <v>70001</v>
       </c>
       <c r="F1036" s="62">
         <v>1</v>
@@ -54196,8 +54196,8 @@
       <c r="D1037" s="62">
         <v>4</v>
       </c>
-      <c r="E1037" s="62">
-        <v>70004</v>
+      <c r="E1037" s="60">
+        <v>70001</v>
       </c>
       <c r="F1037" s="62">
         <v>1</v>
@@ -54246,8 +54246,8 @@
       <c r="D1038" s="62">
         <v>4</v>
       </c>
-      <c r="E1038" s="62">
-        <v>70004</v>
+      <c r="E1038" s="60">
+        <v>70001</v>
       </c>
       <c r="F1038" s="62">
         <v>1</v>
@@ -54296,8 +54296,8 @@
       <c r="D1039" s="62">
         <v>4</v>
       </c>
-      <c r="E1039" s="62">
-        <v>70004</v>
+      <c r="E1039" s="60">
+        <v>70001</v>
       </c>
       <c r="F1039" s="62">
         <v>1</v>
@@ -54346,8 +54346,8 @@
       <c r="D1040" s="67">
         <v>4</v>
       </c>
-      <c r="E1040" s="67">
-        <v>70004</v>
+      <c r="E1040" s="60">
+        <v>70001</v>
       </c>
       <c r="F1040" s="67">
         <v>1</v>
@@ -54396,8 +54396,8 @@
       <c r="D1041" s="62">
         <v>4</v>
       </c>
-      <c r="E1041" s="62">
-        <v>70004</v>
+      <c r="E1041" s="60">
+        <v>70001</v>
       </c>
       <c r="F1041" s="62">
         <v>1</v>
@@ -54446,8 +54446,8 @@
       <c r="D1042" s="62">
         <v>4</v>
       </c>
-      <c r="E1042" s="62">
-        <v>70004</v>
+      <c r="E1042" s="60">
+        <v>70001</v>
       </c>
       <c r="F1042" s="62">
         <v>1</v>
@@ -54496,8 +54496,8 @@
       <c r="D1043" s="62">
         <v>4</v>
       </c>
-      <c r="E1043" s="62">
-        <v>70004</v>
+      <c r="E1043" s="60">
+        <v>70001</v>
       </c>
       <c r="F1043" s="62">
         <v>1</v>
@@ -54546,8 +54546,8 @@
       <c r="D1044" s="62">
         <v>4</v>
       </c>
-      <c r="E1044" s="62">
-        <v>70004</v>
+      <c r="E1044" s="60">
+        <v>70001</v>
       </c>
       <c r="F1044" s="62">
         <v>1</v>
@@ -54596,8 +54596,8 @@
       <c r="D1045" s="62">
         <v>4</v>
       </c>
-      <c r="E1045" s="62">
-        <v>70004</v>
+      <c r="E1045" s="60">
+        <v>70001</v>
       </c>
       <c r="F1045" s="62">
         <v>1</v>
@@ -54646,8 +54646,8 @@
       <c r="D1046" s="62">
         <v>4</v>
       </c>
-      <c r="E1046" s="62">
-        <v>70004</v>
+      <c r="E1046" s="60">
+        <v>70001</v>
       </c>
       <c r="F1046" s="62">
         <v>1</v>
@@ -54696,8 +54696,8 @@
       <c r="D1047" s="62">
         <v>4</v>
       </c>
-      <c r="E1047" s="62">
-        <v>70004</v>
+      <c r="E1047" s="60">
+        <v>70001</v>
       </c>
       <c r="F1047" s="62">
         <v>1</v>
@@ -54746,8 +54746,8 @@
       <c r="D1048" s="62">
         <v>4</v>
       </c>
-      <c r="E1048" s="62">
-        <v>70004</v>
+      <c r="E1048" s="60">
+        <v>70001</v>
       </c>
       <c r="F1048" s="62">
         <v>1</v>
@@ -54796,8 +54796,8 @@
       <c r="D1049" s="69">
         <v>4</v>
       </c>
-      <c r="E1049" s="69">
-        <v>70004</v>
+      <c r="E1049" s="60">
+        <v>70001</v>
       </c>
       <c r="F1049" s="69">
         <v>1</v>
@@ -54846,8 +54846,8 @@
       <c r="D1050" s="62">
         <v>4</v>
       </c>
-      <c r="E1050" s="62">
-        <v>70004</v>
+      <c r="E1050" s="60">
+        <v>70001</v>
       </c>
       <c r="F1050" s="62">
         <v>1</v>
@@ -54896,8 +54896,8 @@
       <c r="D1051" s="62">
         <v>4</v>
       </c>
-      <c r="E1051" s="62">
-        <v>70004</v>
+      <c r="E1051" s="60">
+        <v>70001</v>
       </c>
       <c r="F1051" s="62">
         <v>1</v>
@@ -54946,8 +54946,8 @@
       <c r="D1052" s="62">
         <v>4</v>
       </c>
-      <c r="E1052" s="62">
-        <v>70004</v>
+      <c r="E1052" s="60">
+        <v>70001</v>
       </c>
       <c r="F1052" s="62">
         <v>1</v>
@@ -54996,8 +54996,8 @@
       <c r="D1053" s="62">
         <v>4</v>
       </c>
-      <c r="E1053" s="62">
-        <v>70004</v>
+      <c r="E1053" s="60">
+        <v>70001</v>
       </c>
       <c r="F1053" s="62">
         <v>1</v>
@@ -55046,8 +55046,8 @@
       <c r="D1054" s="62">
         <v>4</v>
       </c>
-      <c r="E1054" s="62">
-        <v>70004</v>
+      <c r="E1054" s="60">
+        <v>70001</v>
       </c>
       <c r="F1054" s="62">
         <v>1</v>
@@ -55096,8 +55096,8 @@
       <c r="D1055" s="62">
         <v>4</v>
       </c>
-      <c r="E1055" s="62">
-        <v>70004</v>
+      <c r="E1055" s="60">
+        <v>70001</v>
       </c>
       <c r="F1055" s="62">
         <v>1</v>
@@ -55146,8 +55146,8 @@
       <c r="D1056" s="62">
         <v>4</v>
       </c>
-      <c r="E1056" s="62">
-        <v>70004</v>
+      <c r="E1056" s="60">
+        <v>70001</v>
       </c>
       <c r="F1056" s="62">
         <v>1</v>
@@ -55196,8 +55196,8 @@
       <c r="D1057" s="62">
         <v>4</v>
       </c>
-      <c r="E1057" s="62">
-        <v>70004</v>
+      <c r="E1057" s="60">
+        <v>70001</v>
       </c>
       <c r="F1057" s="62">
         <v>1</v>
@@ -55246,8 +55246,8 @@
       <c r="D1058" s="62">
         <v>4</v>
       </c>
-      <c r="E1058" s="62">
-        <v>70004</v>
+      <c r="E1058" s="60">
+        <v>70001</v>
       </c>
       <c r="F1058" s="62">
         <v>1</v>
@@ -55296,8 +55296,8 @@
       <c r="D1059" s="69">
         <v>4</v>
       </c>
-      <c r="E1059" s="69">
-        <v>70004</v>
+      <c r="E1059" s="60">
+        <v>70001</v>
       </c>
       <c r="F1059" s="69">
         <v>1</v>
@@ -55346,8 +55346,8 @@
       <c r="D1060" s="62">
         <v>4</v>
       </c>
-      <c r="E1060" s="62">
-        <v>70004</v>
+      <c r="E1060" s="60">
+        <v>70001</v>
       </c>
       <c r="F1060" s="62">
         <v>1</v>
@@ -55396,8 +55396,8 @@
       <c r="D1061" s="62">
         <v>4</v>
       </c>
-      <c r="E1061" s="62">
-        <v>70004</v>
+      <c r="E1061" s="60">
+        <v>70001</v>
       </c>
       <c r="F1061" s="62">
         <v>1</v>
@@ -55446,8 +55446,8 @@
       <c r="D1062" s="62">
         <v>4</v>
       </c>
-      <c r="E1062" s="62">
-        <v>70004</v>
+      <c r="E1062" s="60">
+        <v>70001</v>
       </c>
       <c r="F1062" s="62">
         <v>1</v>
@@ -55496,8 +55496,8 @@
       <c r="D1063" s="62">
         <v>4</v>
       </c>
-      <c r="E1063" s="62">
-        <v>70004</v>
+      <c r="E1063" s="60">
+        <v>70001</v>
       </c>
       <c r="F1063" s="62">
         <v>1</v>
@@ -55546,8 +55546,8 @@
       <c r="D1064" s="62">
         <v>4</v>
       </c>
-      <c r="E1064" s="62">
-        <v>70004</v>
+      <c r="E1064" s="60">
+        <v>70001</v>
       </c>
       <c r="F1064" s="62">
         <v>1</v>
@@ -55596,8 +55596,8 @@
       <c r="D1065" s="62">
         <v>4</v>
       </c>
-      <c r="E1065" s="62">
-        <v>70004</v>
+      <c r="E1065" s="60">
+        <v>70001</v>
       </c>
       <c r="F1065" s="62">
         <v>1</v>
@@ -55646,8 +55646,8 @@
       <c r="D1066" s="62">
         <v>4</v>
       </c>
-      <c r="E1066" s="62">
-        <v>70004</v>
+      <c r="E1066" s="60">
+        <v>70001</v>
       </c>
       <c r="F1066" s="62">
         <v>1</v>
@@ -55696,8 +55696,8 @@
       <c r="D1067" s="62">
         <v>4</v>
       </c>
-      <c r="E1067" s="62">
-        <v>70004</v>
+      <c r="E1067" s="60">
+        <v>70001</v>
       </c>
       <c r="F1067" s="62">
         <v>1</v>
@@ -55746,8 +55746,8 @@
       <c r="D1068" s="62">
         <v>4</v>
       </c>
-      <c r="E1068" s="62">
-        <v>70004</v>
+      <c r="E1068" s="60">
+        <v>70001</v>
       </c>
       <c r="F1068" s="62">
         <v>1</v>
@@ -55796,8 +55796,8 @@
       <c r="D1069" s="62">
         <v>4</v>
       </c>
-      <c r="E1069" s="62">
-        <v>70004</v>
+      <c r="E1069" s="60">
+        <v>70001</v>
       </c>
       <c r="F1069" s="62">
         <v>1</v>
@@ -55846,8 +55846,8 @@
       <c r="D1070" s="62">
         <v>4</v>
       </c>
-      <c r="E1070" s="62">
-        <v>70004</v>
+      <c r="E1070" s="60">
+        <v>70001</v>
       </c>
       <c r="F1070" s="62">
         <v>1</v>
@@ -55896,8 +55896,8 @@
       <c r="D1071" s="69">
         <v>4</v>
       </c>
-      <c r="E1071" s="69">
-        <v>70004</v>
+      <c r="E1071" s="60">
+        <v>70001</v>
       </c>
       <c r="F1071" s="69">
         <v>1</v>
@@ -55946,8 +55946,8 @@
       <c r="D1072" s="62">
         <v>4</v>
       </c>
-      <c r="E1072" s="62">
-        <v>70004</v>
+      <c r="E1072" s="60">
+        <v>70001</v>
       </c>
       <c r="F1072" s="62">
         <v>1</v>
@@ -55996,8 +55996,8 @@
       <c r="D1073" s="62">
         <v>4</v>
       </c>
-      <c r="E1073" s="62">
-        <v>70004</v>
+      <c r="E1073" s="60">
+        <v>70001</v>
       </c>
       <c r="F1073" s="62">
         <v>1</v>
@@ -56046,8 +56046,8 @@
       <c r="D1074" s="62">
         <v>4</v>
       </c>
-      <c r="E1074" s="62">
-        <v>70004</v>
+      <c r="E1074" s="60">
+        <v>70001</v>
       </c>
       <c r="F1074" s="62">
         <v>1</v>
@@ -56096,8 +56096,8 @@
       <c r="D1075" s="62">
         <v>4</v>
       </c>
-      <c r="E1075" s="62">
-        <v>70004</v>
+      <c r="E1075" s="60">
+        <v>70001</v>
       </c>
       <c r="F1075" s="62">
         <v>1</v>
@@ -56146,8 +56146,8 @@
       <c r="D1076" s="62">
         <v>4</v>
       </c>
-      <c r="E1076" s="62">
-        <v>70004</v>
+      <c r="E1076" s="60">
+        <v>70001</v>
       </c>
       <c r="F1076" s="62">
         <v>1</v>
@@ -56196,8 +56196,8 @@
       <c r="D1077" s="62">
         <v>4</v>
       </c>
-      <c r="E1077" s="62">
-        <v>70004</v>
+      <c r="E1077" s="60">
+        <v>70001</v>
       </c>
       <c r="F1077" s="62">
         <v>1</v>
@@ -56246,8 +56246,8 @@
       <c r="D1078" s="62">
         <v>4</v>
       </c>
-      <c r="E1078" s="62">
-        <v>70004</v>
+      <c r="E1078" s="60">
+        <v>70001</v>
       </c>
       <c r="F1078" s="62">
         <v>1</v>
@@ -56296,8 +56296,8 @@
       <c r="D1079" s="62">
         <v>4</v>
       </c>
-      <c r="E1079" s="62">
-        <v>70004</v>
+      <c r="E1079" s="60">
+        <v>70001</v>
       </c>
       <c r="F1079" s="62">
         <v>1</v>
@@ -56346,8 +56346,8 @@
       <c r="D1080" s="62">
         <v>4</v>
       </c>
-      <c r="E1080" s="62">
-        <v>70004</v>
+      <c r="E1080" s="60">
+        <v>70001</v>
       </c>
       <c r="F1080" s="62">
         <v>1</v>
@@ -56396,8 +56396,8 @@
       <c r="D1081" s="62">
         <v>4</v>
       </c>
-      <c r="E1081" s="62">
-        <v>70004</v>
+      <c r="E1081" s="60">
+        <v>70001</v>
       </c>
       <c r="F1081" s="62">
         <v>1</v>
@@ -56446,8 +56446,8 @@
       <c r="D1082" s="62">
         <v>4</v>
       </c>
-      <c r="E1082" s="62">
-        <v>70004</v>
+      <c r="E1082" s="60">
+        <v>70001</v>
       </c>
       <c r="F1082" s="62">
         <v>1</v>
@@ -56496,8 +56496,8 @@
       <c r="D1083" s="62">
         <v>4</v>
       </c>
-      <c r="E1083" s="62">
-        <v>70004</v>
+      <c r="E1083" s="60">
+        <v>70001</v>
       </c>
       <c r="F1083" s="62">
         <v>1</v>
@@ -56546,8 +56546,8 @@
       <c r="D1084" s="69">
         <v>4</v>
       </c>
-      <c r="E1084" s="69">
-        <v>70004</v>
+      <c r="E1084" s="60">
+        <v>70001</v>
       </c>
       <c r="F1084" s="69">
         <v>1</v>
@@ -56596,8 +56596,8 @@
       <c r="D1085" s="62">
         <v>4</v>
       </c>
-      <c r="E1085" s="62">
-        <v>70004</v>
+      <c r="E1085" s="60">
+        <v>70001</v>
       </c>
       <c r="F1085" s="62">
         <v>1</v>
@@ -56646,8 +56646,8 @@
       <c r="D1086" s="62">
         <v>4</v>
       </c>
-      <c r="E1086" s="62">
-        <v>70004</v>
+      <c r="E1086" s="60">
+        <v>70001</v>
       </c>
       <c r="F1086" s="62">
         <v>1</v>
@@ -56696,8 +56696,8 @@
       <c r="D1087" s="62">
         <v>4</v>
       </c>
-      <c r="E1087" s="62">
-        <v>70004</v>
+      <c r="E1087" s="60">
+        <v>70001</v>
       </c>
       <c r="F1087" s="62">
         <v>1</v>
@@ -56746,8 +56746,8 @@
       <c r="D1088" s="62">
         <v>4</v>
       </c>
-      <c r="E1088" s="62">
-        <v>70004</v>
+      <c r="E1088" s="60">
+        <v>70001</v>
       </c>
       <c r="F1088" s="62">
         <v>1</v>
@@ -56796,8 +56796,8 @@
       <c r="D1089" s="62">
         <v>4</v>
       </c>
-      <c r="E1089" s="62">
-        <v>70004</v>
+      <c r="E1089" s="60">
+        <v>70001</v>
       </c>
       <c r="F1089" s="62">
         <v>1</v>
@@ -56846,8 +56846,8 @@
       <c r="D1090" s="62">
         <v>4</v>
       </c>
-      <c r="E1090" s="62">
-        <v>70004</v>
+      <c r="E1090" s="60">
+        <v>70001</v>
       </c>
       <c r="F1090" s="62">
         <v>1</v>
@@ -56896,8 +56896,8 @@
       <c r="D1091" s="62">
         <v>4</v>
       </c>
-      <c r="E1091" s="62">
-        <v>70004</v>
+      <c r="E1091" s="60">
+        <v>70001</v>
       </c>
       <c r="F1091" s="62">
         <v>1</v>
@@ -56946,8 +56946,8 @@
       <c r="D1092" s="62">
         <v>4</v>
       </c>
-      <c r="E1092" s="62">
-        <v>70004</v>
+      <c r="E1092" s="60">
+        <v>70001</v>
       </c>
       <c r="F1092" s="62">
         <v>1</v>
@@ -56996,8 +56996,8 @@
       <c r="D1093" s="62">
         <v>4</v>
       </c>
-      <c r="E1093" s="62">
-        <v>70004</v>
+      <c r="E1093" s="60">
+        <v>70001</v>
       </c>
       <c r="F1093" s="62">
         <v>1</v>
@@ -57046,8 +57046,8 @@
       <c r="D1094" s="62">
         <v>4</v>
       </c>
-      <c r="E1094" s="62">
-        <v>70004</v>
+      <c r="E1094" s="60">
+        <v>70001</v>
       </c>
       <c r="F1094" s="62">
         <v>1</v>
@@ -57096,8 +57096,8 @@
       <c r="D1095" s="62">
         <v>4</v>
       </c>
-      <c r="E1095" s="62">
-        <v>70004</v>
+      <c r="E1095" s="60">
+        <v>70001</v>
       </c>
       <c r="F1095" s="62">
         <v>1</v>
@@ -57146,8 +57146,8 @@
       <c r="D1096" s="62">
         <v>4</v>
       </c>
-      <c r="E1096" s="62">
-        <v>70004</v>
+      <c r="E1096" s="60">
+        <v>70001</v>
       </c>
       <c r="F1096" s="62">
         <v>1</v>
@@ -57196,8 +57196,8 @@
       <c r="D1097" s="62">
         <v>4</v>
       </c>
-      <c r="E1097" s="62">
-        <v>70004</v>
+      <c r="E1097" s="60">
+        <v>70001</v>
       </c>
       <c r="F1097" s="62">
         <v>1</v>
@@ -57246,8 +57246,8 @@
       <c r="D1098" s="69">
         <v>4</v>
       </c>
-      <c r="E1098" s="69">
-        <v>70004</v>
+      <c r="E1098" s="60">
+        <v>70001</v>
       </c>
       <c r="F1098" s="69">
         <v>1</v>
@@ -57296,8 +57296,8 @@
       <c r="D1099" s="62">
         <v>4</v>
       </c>
-      <c r="E1099" s="62">
-        <v>70004</v>
+      <c r="E1099" s="60">
+        <v>70001</v>
       </c>
       <c r="F1099" s="62">
         <v>1</v>
@@ -57346,8 +57346,8 @@
       <c r="D1100" s="62">
         <v>4</v>
       </c>
-      <c r="E1100" s="62">
-        <v>70004</v>
+      <c r="E1100" s="60">
+        <v>70001</v>
       </c>
       <c r="F1100" s="62">
         <v>1</v>
@@ -57396,8 +57396,8 @@
       <c r="D1101" s="62">
         <v>4</v>
       </c>
-      <c r="E1101" s="62">
-        <v>70004</v>
+      <c r="E1101" s="60">
+        <v>70001</v>
       </c>
       <c r="F1101" s="62">
         <v>1</v>
@@ -57446,8 +57446,8 @@
       <c r="D1102" s="62">
         <v>4</v>
       </c>
-      <c r="E1102" s="62">
-        <v>70004</v>
+      <c r="E1102" s="60">
+        <v>70001</v>
       </c>
       <c r="F1102" s="62">
         <v>1</v>
@@ -57496,8 +57496,8 @@
       <c r="D1103" s="62">
         <v>4</v>
       </c>
-      <c r="E1103" s="62">
-        <v>70004</v>
+      <c r="E1103" s="60">
+        <v>70001</v>
       </c>
       <c r="F1103" s="62">
         <v>1</v>
@@ -57546,8 +57546,8 @@
       <c r="D1104" s="62">
         <v>4</v>
       </c>
-      <c r="E1104" s="62">
-        <v>70004</v>
+      <c r="E1104" s="60">
+        <v>70001</v>
       </c>
       <c r="F1104" s="62">
         <v>1</v>
@@ -57596,8 +57596,8 @@
       <c r="D1105" s="62">
         <v>4</v>
       </c>
-      <c r="E1105" s="62">
-        <v>70004</v>
+      <c r="E1105" s="60">
+        <v>70001</v>
       </c>
       <c r="F1105" s="62">
         <v>1</v>
@@ -57646,8 +57646,8 @@
       <c r="D1106" s="62">
         <v>4</v>
       </c>
-      <c r="E1106" s="62">
-        <v>70004</v>
+      <c r="E1106" s="60">
+        <v>70001</v>
       </c>
       <c r="F1106" s="62">
         <v>1</v>
@@ -57696,8 +57696,8 @@
       <c r="D1107" s="62">
         <v>4</v>
       </c>
-      <c r="E1107" s="62">
-        <v>70004</v>
+      <c r="E1107" s="60">
+        <v>70001</v>
       </c>
       <c r="F1107" s="62">
         <v>1</v>
@@ -57746,8 +57746,8 @@
       <c r="D1108" s="62">
         <v>4</v>
       </c>
-      <c r="E1108" s="62">
-        <v>70004</v>
+      <c r="E1108" s="60">
+        <v>70001</v>
       </c>
       <c r="F1108" s="62">
         <v>1</v>
@@ -57796,8 +57796,8 @@
       <c r="D1109" s="62">
         <v>4</v>
       </c>
-      <c r="E1109" s="62">
-        <v>70004</v>
+      <c r="E1109" s="60">
+        <v>70001</v>
       </c>
       <c r="F1109" s="62">
         <v>1</v>
@@ -57846,8 +57846,8 @@
       <c r="D1110" s="62">
         <v>4</v>
       </c>
-      <c r="E1110" s="62">
-        <v>70004</v>
+      <c r="E1110" s="60">
+        <v>70001</v>
       </c>
       <c r="F1110" s="62">
         <v>1</v>
@@ -57896,8 +57896,8 @@
       <c r="D1111" s="62">
         <v>4</v>
       </c>
-      <c r="E1111" s="62">
-        <v>70004</v>
+      <c r="E1111" s="60">
+        <v>70001</v>
       </c>
       <c r="F1111" s="62">
         <v>1</v>
@@ -57946,8 +57946,8 @@
       <c r="D1112" s="62">
         <v>4</v>
       </c>
-      <c r="E1112" s="62">
-        <v>70004</v>
+      <c r="E1112" s="60">
+        <v>70001</v>
       </c>
       <c r="F1112" s="62">
         <v>1</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_brush_foe_v8【迷宫-刷怪相关时间数量类型】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2678E7-527A-485D-84C8-5E358306411A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A76BF84-1768-4CDE-BB04-BFA194F64E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="806">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -2463,18 +2463,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>50,70,50,50</t>
-  </si>
-  <si>
-    <t>50,50</t>
-  </si>
-  <si>
-    <t>5,40,75,20</t>
-  </si>
-  <si>
-    <t>95,30,25,10</t>
-  </si>
-  <si>
     <t>30,80</t>
   </si>
   <si>
@@ -2505,16 +2493,73 @@
     <t>91105,91105</t>
   </si>
   <si>
-    <t>91106,91106</t>
-  </si>
-  <si>
-    <t>91105,91105,91105</t>
-  </si>
-  <si>
-    <t>91106,91105</t>
-  </si>
-  <si>
-    <t>91106,91106,91105</t>
+    <t>50,55</t>
+  </si>
+  <si>
+    <t>50,50,50,40</t>
+  </si>
+  <si>
+    <t>50,30</t>
+  </si>
+  <si>
+    <t>5,20</t>
+  </si>
+  <si>
+    <t>95,15,25,10,75,15</t>
+  </si>
+  <si>
+    <t>91101</t>
+  </si>
+  <si>
+    <t>91102,91102</t>
+  </si>
+  <si>
+    <t>91103</t>
+  </si>
+  <si>
+    <t>91103,91104,91104</t>
+  </si>
+  <si>
+    <t>91101,91101,91101</t>
+  </si>
+  <si>
+    <t>91102,91101</t>
+  </si>
+  <si>
+    <t>91102,91102,91101</t>
+  </si>
+  <si>
+    <t>10,45</t>
+  </si>
+  <si>
+    <t>10,55,35,65</t>
+  </si>
+  <si>
+    <t>10,60</t>
+  </si>
+  <si>
+    <t>55,62</t>
+  </si>
+  <si>
+    <t>45,75,45,95</t>
+  </si>
+  <si>
+    <t>70,95,80,95</t>
+  </si>
+  <si>
+    <t>111101</t>
+  </si>
+  <si>
+    <t>111101,111104</t>
+  </si>
+  <si>
+    <t>111102</t>
+  </si>
+  <si>
+    <t>111102,111105</t>
+  </si>
+  <si>
+    <t>111105,111105</t>
   </si>
 </sst>
 </file>
@@ -3327,7 +3372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE4854-7B6A-484A-9D3D-BA7D302B22E8}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R1081"/>
+  <dimension ref="A1:R1087"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="14.625" style="1" customWidth="1"/>
@@ -63081,7 +63126,7 @@
         <v>1</v>
       </c>
       <c r="J1068" s="2" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="K1068" s="1">
         <v>100</v>
@@ -63096,7 +63141,7 @@
         <v>0</v>
       </c>
       <c r="O1068" s="1" t="s">
-        <v>166</v>
+        <v>783</v>
       </c>
       <c r="P1068" s="1">
         <v>0</v>
@@ -63131,7 +63176,7 @@
         <v>1</v>
       </c>
       <c r="J1069" s="2" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="K1069" s="1">
         <v>100</v>
@@ -63146,7 +63191,7 @@
         <v>0</v>
       </c>
       <c r="O1069" s="1" t="s">
-        <v>773</v>
+        <v>784</v>
       </c>
       <c r="P1069" s="1">
         <v>0</v>
@@ -63181,7 +63226,7 @@
         <v>1</v>
       </c>
       <c r="J1070" s="2" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="K1070" s="1">
         <v>100</v>
@@ -63196,7 +63241,7 @@
         <v>0</v>
       </c>
       <c r="O1070" s="1" t="s">
-        <v>164</v>
+        <v>785</v>
       </c>
       <c r="P1070" s="1">
         <v>0</v>
@@ -63231,7 +63276,7 @@
         <v>2</v>
       </c>
       <c r="J1071" s="2" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="K1071" s="1">
         <v>100</v>
@@ -63246,7 +63291,7 @@
         <v>0</v>
       </c>
       <c r="O1071" s="1" t="s">
-        <v>774</v>
+        <v>785</v>
       </c>
       <c r="P1071" s="1">
         <v>0</v>
@@ -63255,7 +63300,7 @@
         <v>0</v>
       </c>
       <c r="R1071" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1072" spans="1:18" x14ac:dyDescent="0.2">
@@ -63281,7 +63326,7 @@
         <v>2</v>
       </c>
       <c r="J1072" s="2" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="K1072" s="1">
         <v>100</v>
@@ -63296,7 +63341,7 @@
         <v>0</v>
       </c>
       <c r="O1072" s="1" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="P1072" s="1">
         <v>0</v>
@@ -63305,7 +63350,7 @@
         <v>0</v>
       </c>
       <c r="R1072" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1073" spans="1:18" x14ac:dyDescent="0.2">
@@ -63331,7 +63376,7 @@
         <v>2</v>
       </c>
       <c r="J1073" s="2" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="K1073" s="1">
         <v>100</v>
@@ -63346,7 +63391,7 @@
         <v>0</v>
       </c>
       <c r="O1073" s="1" t="s">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="P1073" s="1">
         <v>0</v>
@@ -63381,7 +63426,7 @@
         <v>3</v>
       </c>
       <c r="J1074" s="2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="K1074" s="1">
         <v>100</v>
@@ -63396,7 +63441,7 @@
         <v>1</v>
       </c>
       <c r="O1074" s="1" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="P1074" s="1">
         <v>0</v>
@@ -63431,7 +63476,7 @@
         <v>3</v>
       </c>
       <c r="J1075" s="2" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="K1075" s="1">
         <v>100</v>
@@ -63446,7 +63491,7 @@
         <v>1</v>
       </c>
       <c r="O1075" s="1" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="P1075" s="1">
         <v>0</v>
@@ -63481,7 +63526,7 @@
         <v>3</v>
       </c>
       <c r="J1076" s="2" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="K1076" s="1">
         <v>100</v>
@@ -63496,7 +63541,7 @@
         <v>1</v>
       </c>
       <c r="O1076" s="1" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="P1076" s="1">
         <v>0</v>
@@ -63531,7 +63576,7 @@
         <v>3</v>
       </c>
       <c r="J1077" s="2" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="K1077" s="1">
         <v>100</v>
@@ -63546,7 +63591,7 @@
         <v>1</v>
       </c>
       <c r="O1077" s="1" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="P1077" s="1">
         <v>0</v>
@@ -63581,7 +63626,7 @@
         <v>4</v>
       </c>
       <c r="J1078" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="K1078" s="1">
         <v>100</v>
@@ -63596,7 +63641,7 @@
         <v>1</v>
       </c>
       <c r="O1078" s="1" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="P1078" s="1">
         <v>0</v>
@@ -63631,7 +63676,7 @@
         <v>4</v>
       </c>
       <c r="J1079" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="K1079" s="1">
         <v>100</v>
@@ -63646,7 +63691,7 @@
         <v>1</v>
       </c>
       <c r="O1079" s="1" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="P1079" s="1">
         <v>0</v>
@@ -63681,7 +63726,7 @@
         <v>4</v>
       </c>
       <c r="J1080" s="2" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="K1080" s="1">
         <v>100</v>
@@ -63696,7 +63741,7 @@
         <v>1</v>
       </c>
       <c r="O1080" s="1" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="P1080" s="1">
         <v>0</v>
@@ -63731,7 +63776,7 @@
         <v>4</v>
       </c>
       <c r="J1081" s="2" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="K1081" s="1">
         <v>100</v>
@@ -63746,7 +63791,7 @@
         <v>1</v>
       </c>
       <c r="O1081" s="1" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="P1081" s="1">
         <v>0</v>
@@ -63755,6 +63800,306 @@
         <v>0</v>
       </c>
       <c r="R1081" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1082" s="1">
+        <v>1110101</v>
+      </c>
+      <c r="B1082" s="1">
+        <v>11</v>
+      </c>
+      <c r="E1082" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1082" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1082" s="1">
+        <v>1</v>
+      </c>
+      <c r="H1082" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1082" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1082" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="K1082" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1082" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1082" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1082" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1082" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="P1082" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1082" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1082" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1083" s="1">
+        <v>1110102</v>
+      </c>
+      <c r="B1083" s="1">
+        <v>11</v>
+      </c>
+      <c r="E1083" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1083" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1083" s="1">
+        <v>2</v>
+      </c>
+      <c r="H1083" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1083" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1083" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="K1083" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1083" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1083" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1083" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1083" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="P1083" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1083" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1083" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1084" s="1">
+        <v>1110103</v>
+      </c>
+      <c r="B1084" s="1">
+        <v>11</v>
+      </c>
+      <c r="E1084" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1084" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1084" s="1">
+        <v>3</v>
+      </c>
+      <c r="H1084" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1084" s="1">
+        <v>1</v>
+      </c>
+      <c r="J1084" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="K1084" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1084" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1084" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1084" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1084" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="P1084" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1084" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1084" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1085" s="1">
+        <v>1110201</v>
+      </c>
+      <c r="B1085" s="1">
+        <v>11</v>
+      </c>
+      <c r="E1085" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1085" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1085" s="1">
+        <v>4</v>
+      </c>
+      <c r="H1085" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1085" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1085" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="K1085" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1085" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1085" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1085" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1085" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="P1085" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1085" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1085" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1086" s="1">
+        <v>1110202</v>
+      </c>
+      <c r="B1086" s="1">
+        <v>11</v>
+      </c>
+      <c r="E1086" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1086" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1086" s="1">
+        <v>5</v>
+      </c>
+      <c r="H1086" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I1086" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1086" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="K1086" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1086" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1086" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1086" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1086" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="P1086" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1086" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1086" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1087" s="1">
+        <v>1110203</v>
+      </c>
+      <c r="B1087" s="1">
+        <v>11</v>
+      </c>
+      <c r="E1087" s="1">
+        <v>110001</v>
+      </c>
+      <c r="F1087" s="1">
+        <v>1</v>
+      </c>
+      <c r="G1087" s="1">
+        <v>6</v>
+      </c>
+      <c r="H1087" s="1">
+        <v>1</v>
+      </c>
+      <c r="I1087" s="1">
+        <v>2</v>
+      </c>
+      <c r="J1087" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="K1087" s="1">
+        <v>150</v>
+      </c>
+      <c r="L1087" s="1">
+        <v>30000</v>
+      </c>
+      <c r="M1087" s="1">
+        <v>0</v>
+      </c>
+      <c r="N1087" s="1">
+        <v>0</v>
+      </c>
+      <c r="O1087" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="P1087" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q1087" s="1">
+        <v>0</v>
+      </c>
+      <c r="R1087" s="1">
         <v>0</v>
       </c>
     </row>
